--- a/research/traditional_assets/database/data/canada/canada_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_food_wholesalers.xlsx
@@ -1212,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1349,22 +1349,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06764135753004567</v>
+        <v>0.06749518293259105</v>
       </c>
       <c r="C2">
-        <v>141.0041081473726</v>
+        <v>139.838433923499</v>
       </c>
       <c r="D2">
-        <v>139.2741081473726</v>
+        <v>139.985433923499</v>
       </c>
       <c r="E2">
-        <v>-123.9</v>
+        <v>-122.023</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.877</v>
       </c>
       <c r="G2">
         <v>1.73</v>
@@ -1385,28 +1385,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0944131</v>
       </c>
       <c r="N2">
-        <v>7.200000000000001</v>
+        <v>7.105586900000001</v>
       </c>
       <c r="O2">
-        <v>1.908</v>
+        <v>1.882980528500001</v>
       </c>
       <c r="P2">
-        <v>5.292000000000001</v>
+        <v>5.222606371500001</v>
       </c>
       <c r="Q2">
-        <v>20.892</v>
+        <v>20.8226063715</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06764135753004567</v>
+        <v>0.06780351306322328</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.508164273977443</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>76.26060366622853</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06749518293259105</v>
+        <v>0.06734900833513642</v>
       </c>
       <c r="C3">
-        <v>139.838433923499</v>
+        <v>138.6800630223665</v>
       </c>
       <c r="D3">
-        <v>139.985433923499</v>
+        <v>140.7040630223665</v>
       </c>
       <c r="E3">
-        <v>-122.023</v>
+        <v>-120.146</v>
       </c>
       <c r="F3">
-        <v>1.877</v>
+        <v>3.754</v>
       </c>
       <c r="G3">
         <v>1.73</v>
@@ -1467,28 +1467,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0944131</v>
+        <v>0.1888262</v>
       </c>
       <c r="N3">
-        <v>7.105586900000001</v>
+        <v>7.011173800000001</v>
       </c>
       <c r="O3">
-        <v>1.882980528500001</v>
+        <v>1.857961057</v>
       </c>
       <c r="P3">
-        <v>5.222606371500001</v>
+        <v>5.153212743000001</v>
       </c>
       <c r="Q3">
-        <v>20.8226063715</v>
+        <v>20.753212743</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06780351306322328</v>
+        <v>0.06796897789299636</v>
       </c>
       <c r="T3">
-        <v>0.508164273977443</v>
+        <v>0.5119856326327102</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>76.26060366622853</v>
+        <v>38.13030183311427</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1513,22 +1513,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06734900833513642</v>
+        <v>0.06720283373768179</v>
       </c>
       <c r="C4">
-        <v>138.6800630223665</v>
+        <v>137.5291085013598</v>
       </c>
       <c r="D4">
-        <v>140.7040630223665</v>
+        <v>141.4301085013598</v>
       </c>
       <c r="E4">
-        <v>-120.146</v>
+        <v>-118.269</v>
       </c>
       <c r="F4">
-        <v>3.754</v>
+        <v>5.630999999999999</v>
       </c>
       <c r="G4">
         <v>1.73</v>
@@ -1549,28 +1549,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M4">
-        <v>0.1888262</v>
+        <v>0.2832393</v>
       </c>
       <c r="N4">
-        <v>7.011173800000001</v>
+        <v>6.916760700000001</v>
       </c>
       <c r="O4">
-        <v>1.857961057</v>
+        <v>1.8329415855</v>
       </c>
       <c r="P4">
-        <v>5.153212743000001</v>
+        <v>5.083819114500001</v>
       </c>
       <c r="Q4">
-        <v>20.753212743</v>
+        <v>20.6838191145</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06796897789299636</v>
+        <v>0.06813785436874413</v>
       </c>
       <c r="T4">
-        <v>0.5119856326327102</v>
+        <v>0.5158857821880862</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.13030183311427</v>
+        <v>25.42020122207618</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1595,22 +1595,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06720283373768179</v>
+        <v>0.06705665914022718</v>
       </c>
       <c r="C5">
-        <v>137.5291085013598</v>
+        <v>136.3856857635117</v>
       </c>
       <c r="D5">
-        <v>141.4301085013598</v>
+        <v>142.1636857635117</v>
       </c>
       <c r="E5">
-        <v>-118.269</v>
+        <v>-116.392</v>
       </c>
       <c r="F5">
-        <v>5.630999999999999</v>
+        <v>7.508</v>
       </c>
       <c r="G5">
         <v>1.73</v>
@@ -1631,28 +1631,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M5">
-        <v>0.2832393</v>
+        <v>0.3776524</v>
       </c>
       <c r="N5">
-        <v>6.916760700000001</v>
+        <v>6.822347600000001</v>
       </c>
       <c r="O5">
-        <v>1.8329415855</v>
+        <v>1.807922114</v>
       </c>
       <c r="P5">
-        <v>5.083819114500001</v>
+        <v>5.014425486000001</v>
       </c>
       <c r="Q5">
-        <v>20.6838191145</v>
+        <v>20.614425486</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06813785436874413</v>
+        <v>0.06831024910440331</v>
       </c>
       <c r="T5">
-        <v>0.5158857821880862</v>
+        <v>0.519867184859199</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.42020122207618</v>
+        <v>19.06515091655713</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1677,22 +1677,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06705665914022718</v>
+        <v>0.06691048454277257</v>
       </c>
       <c r="C6">
-        <v>136.3856857635117</v>
+        <v>135.2499126186538</v>
       </c>
       <c r="D6">
-        <v>142.1636857635117</v>
+        <v>142.9049126186538</v>
       </c>
       <c r="E6">
-        <v>-116.392</v>
+        <v>-114.515</v>
       </c>
       <c r="F6">
-        <v>7.508</v>
+        <v>9.385</v>
       </c>
       <c r="G6">
         <v>1.73</v>
@@ -1713,28 +1713,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M6">
-        <v>0.3776524</v>
+        <v>0.4720655</v>
       </c>
       <c r="N6">
-        <v>6.822347600000001</v>
+        <v>6.727934500000001</v>
       </c>
       <c r="O6">
-        <v>1.807922114</v>
+        <v>1.7829026425</v>
       </c>
       <c r="P6">
-        <v>5.014425486000001</v>
+        <v>4.9450318575</v>
       </c>
       <c r="Q6">
-        <v>20.614425486</v>
+        <v>20.5450318575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.06831024910440331</v>
+        <v>0.06848627320291849</v>
       </c>
       <c r="T6">
-        <v>0.519867184859199</v>
+        <v>0.5239324065339144</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.06515091655713</v>
+        <v>15.25212073324571</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1759,22 +1759,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06691048454277257</v>
+        <v>0.06683045994531794</v>
       </c>
       <c r="C7">
-        <v>135.2499126186538</v>
+        <v>133.7819873389674</v>
       </c>
       <c r="D7">
-        <v>142.9049126186538</v>
+        <v>143.3139873389674</v>
       </c>
       <c r="E7">
-        <v>-114.515</v>
+        <v>-112.638</v>
       </c>
       <c r="F7">
-        <v>9.385</v>
+        <v>11.262</v>
       </c>
       <c r="G7">
         <v>1.73</v>
@@ -1795,45 +1795,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M7">
-        <v>0.4720655</v>
+        <v>0.5833716</v>
       </c>
       <c r="N7">
-        <v>6.727934500000001</v>
+        <v>6.616628400000002</v>
       </c>
       <c r="O7">
-        <v>1.7829026425</v>
+        <v>1.753406526</v>
       </c>
       <c r="P7">
-        <v>4.9450318575</v>
+        <v>4.863221874000001</v>
       </c>
       <c r="Q7">
-        <v>20.5450318575</v>
+        <v>20.463221874</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06848627320291849</v>
+        <v>0.06866604249501909</v>
       </c>
       <c r="T7">
-        <v>0.5239324065339144</v>
+        <v>0.5280841222868151</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.265</v>
       </c>
       <c r="W7">
-        <v>0.0369705</v>
+        <v>0.038073</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>15.25212073324571</v>
+        <v>12.34204750454085</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1841,22 +1841,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06683045994531794</v>
+        <v>0.06669531034786333</v>
       </c>
       <c r="C8">
-        <v>133.7819873389674</v>
+        <v>132.6011969043949</v>
       </c>
       <c r="D8">
-        <v>143.3139873389674</v>
+        <v>144.0101969043949</v>
       </c>
       <c r="E8">
-        <v>-112.638</v>
+        <v>-110.761</v>
       </c>
       <c r="F8">
-        <v>11.262</v>
+        <v>13.139</v>
       </c>
       <c r="G8">
         <v>1.73</v>
@@ -1877,28 +1877,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M8">
-        <v>0.5833715999999999</v>
+        <v>0.6806001999999999</v>
       </c>
       <c r="N8">
-        <v>6.616628400000002</v>
+        <v>6.519399800000001</v>
       </c>
       <c r="O8">
-        <v>1.753406526</v>
+        <v>1.727640947</v>
       </c>
       <c r="P8">
-        <v>4.863221874000001</v>
+        <v>4.791758853000001</v>
       </c>
       <c r="Q8">
-        <v>20.463221874</v>
+        <v>20.391758853</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06866604249501909</v>
+        <v>0.06884967779340143</v>
       </c>
       <c r="T8">
-        <v>0.528084122286815</v>
+        <v>0.5323251222494556</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.34204750454085</v>
+        <v>10.57889786103501</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1923,22 +1923,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06669531034786332</v>
+        <v>0.06666012075040871</v>
       </c>
       <c r="C9">
-        <v>132.601196904395</v>
+        <v>130.906583901636</v>
       </c>
       <c r="D9">
-        <v>144.010196904395</v>
+        <v>144.192583901636</v>
       </c>
       <c r="E9">
-        <v>-110.761</v>
+        <v>-108.884</v>
       </c>
       <c r="F9">
-        <v>13.139</v>
+        <v>15.016</v>
       </c>
       <c r="G9">
         <v>1.73</v>
@@ -1959,45 +1959,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M9">
-        <v>0.6806002</v>
+        <v>0.803356</v>
       </c>
       <c r="N9">
-        <v>6.519399800000001</v>
+        <v>6.396644000000001</v>
       </c>
       <c r="O9">
-        <v>1.727640947</v>
+        <v>1.69511066</v>
       </c>
       <c r="P9">
-        <v>4.791758853000001</v>
+        <v>4.701533340000001</v>
       </c>
       <c r="Q9">
-        <v>20.391758853</v>
+        <v>20.30153334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06884967779340143</v>
+        <v>0.06903730516348772</v>
       </c>
       <c r="T9">
-        <v>0.5323251222494556</v>
+        <v>0.5366583178634577</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.265</v>
       </c>
       <c r="W9">
-        <v>0.038073</v>
+        <v>0.0393225</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.57889786103501</v>
+        <v>8.962402720587139</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2005,22 +2005,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06666012075040871</v>
+        <v>0.06653746615295408</v>
       </c>
       <c r="C10">
-        <v>130.906583901636</v>
+        <v>129.6689277237111</v>
       </c>
       <c r="D10">
-        <v>144.192583901636</v>
+        <v>144.8319277237111</v>
       </c>
       <c r="E10">
-        <v>-108.884</v>
+        <v>-107.007</v>
       </c>
       <c r="F10">
-        <v>15.016</v>
+        <v>16.893</v>
       </c>
       <c r="G10">
         <v>1.73</v>
@@ -2041,28 +2041,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M10">
-        <v>0.803356</v>
+        <v>0.9037754999999998</v>
       </c>
       <c r="N10">
-        <v>6.396644000000001</v>
+        <v>6.296224500000001</v>
       </c>
       <c r="O10">
-        <v>1.69511066</v>
+        <v>1.6684994925</v>
       </c>
       <c r="P10">
-        <v>4.701533340000001</v>
+        <v>4.6277250075</v>
       </c>
       <c r="Q10">
-        <v>20.30153334</v>
+        <v>20.2277250075</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06903730516348772</v>
+        <v>0.06922905621203745</v>
       </c>
       <c r="T10">
-        <v>0.5366583178634577</v>
+        <v>0.5410867485458996</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.962402720587139</v>
+        <v>7.966580196077458</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2087,22 +2087,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06653746615295408</v>
+        <v>0.06647361155549947</v>
       </c>
       <c r="C11">
-        <v>129.6689277237111</v>
+        <v>128.1270226546222</v>
       </c>
       <c r="D11">
-        <v>144.8319277237111</v>
+        <v>145.1670226546222</v>
       </c>
       <c r="E11">
-        <v>-107.007</v>
+        <v>-105.13</v>
       </c>
       <c r="F11">
-        <v>16.893</v>
+        <v>18.77</v>
       </c>
       <c r="G11">
         <v>1.73</v>
@@ -2123,45 +2123,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M11">
-        <v>0.9037754999999998</v>
+        <v>1.019211</v>
       </c>
       <c r="N11">
-        <v>6.296224500000001</v>
+        <v>6.180789000000001</v>
       </c>
       <c r="O11">
-        <v>1.6684994925</v>
+        <v>1.637909085</v>
       </c>
       <c r="P11">
-        <v>4.6277250075</v>
+        <v>4.542879915</v>
       </c>
       <c r="Q11">
-        <v>20.2277250075</v>
+        <v>20.142879915</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06922905621203745</v>
+        <v>0.0694250683949994</v>
       </c>
       <c r="T11">
-        <v>0.5410867485458996</v>
+        <v>0.5456135887990623</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.265</v>
       </c>
       <c r="W11">
-        <v>0.0393225</v>
+        <v>0.0399105</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.966580196077458</v>
+        <v>7.064287963925038</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2169,22 +2169,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06647361155549947</v>
+        <v>0.06635683695804484</v>
       </c>
       <c r="C12">
-        <v>128.1270226546222</v>
+        <v>126.8668579175961</v>
       </c>
       <c r="D12">
-        <v>145.1670226546222</v>
+        <v>145.7838579175962</v>
       </c>
       <c r="E12">
-        <v>-105.13</v>
+        <v>-103.253</v>
       </c>
       <c r="F12">
-        <v>18.77</v>
+        <v>20.647</v>
       </c>
       <c r="G12">
         <v>1.73</v>
@@ -2205,28 +2205,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M12">
-        <v>1.019211</v>
+        <v>1.1211321</v>
       </c>
       <c r="N12">
-        <v>6.180789000000001</v>
+        <v>6.078867900000001</v>
       </c>
       <c r="O12">
-        <v>1.637909085</v>
+        <v>1.610899993500001</v>
       </c>
       <c r="P12">
-        <v>4.542879915</v>
+        <v>4.467967906500001</v>
       </c>
       <c r="Q12">
-        <v>20.142879915</v>
+        <v>20.0679679065</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0694250683949994</v>
+        <v>0.06962548534611779</v>
       </c>
       <c r="T12">
-        <v>0.5456135887990623</v>
+        <v>0.5502421557994872</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.064287963925036</v>
+        <v>6.422079967204581</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2251,22 +2251,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06635683695804484</v>
+        <v>0.06632826236059022</v>
       </c>
       <c r="C13">
-        <v>126.8668579175961</v>
+        <v>125.1415958637904</v>
       </c>
       <c r="D13">
-        <v>145.7838579175962</v>
+        <v>145.9355958637904</v>
       </c>
       <c r="E13">
-        <v>-103.253</v>
+        <v>-101.376</v>
       </c>
       <c r="F13">
-        <v>20.647</v>
+        <v>22.524</v>
       </c>
       <c r="G13">
         <v>1.73</v>
@@ -2287,45 +2287,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M13">
-        <v>1.1211321</v>
+        <v>1.2455772</v>
       </c>
       <c r="N13">
-        <v>6.078867900000001</v>
+        <v>5.954422800000001</v>
       </c>
       <c r="O13">
-        <v>1.610899993500001</v>
+        <v>1.577922042</v>
       </c>
       <c r="P13">
-        <v>4.467967906500001</v>
+        <v>4.376500758000001</v>
       </c>
       <c r="Q13">
-        <v>20.0679679065</v>
+        <v>19.976500758</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06962548534611779</v>
+        <v>0.06983045722794343</v>
       </c>
       <c r="T13">
-        <v>0.5502421557994872</v>
+        <v>0.5549759175044672</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.265</v>
       </c>
       <c r="W13">
-        <v>0.0399105</v>
+        <v>0.0406455</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.422079967204581</v>
+        <v>5.780452628709005</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06632826236059022</v>
+        <v>0.06621883776313559</v>
       </c>
       <c r="C14">
-        <v>125.1415958637904</v>
+        <v>123.848599190759</v>
       </c>
       <c r="D14">
-        <v>145.9355958637904</v>
+        <v>146.519599190759</v>
       </c>
       <c r="E14">
-        <v>-101.376</v>
+        <v>-99.49900000000001</v>
       </c>
       <c r="F14">
-        <v>22.524</v>
+        <v>24.401</v>
       </c>
       <c r="G14">
         <v>1.73</v>
@@ -2369,28 +2369,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M14">
-        <v>1.2455772</v>
+        <v>1.3493753</v>
       </c>
       <c r="N14">
-        <v>5.954422800000001</v>
+        <v>5.850624700000001</v>
       </c>
       <c r="O14">
-        <v>1.577922042</v>
+        <v>1.5504155455</v>
       </c>
       <c r="P14">
-        <v>4.376500758000001</v>
+        <v>4.300209154500001</v>
       </c>
       <c r="Q14">
-        <v>19.976500758</v>
+        <v>19.9002091545</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06983045722794343</v>
+        <v>0.07004014110705241</v>
       </c>
       <c r="T14">
-        <v>0.5549759175044672</v>
+        <v>0.5598185013176076</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.780452628709005</v>
+        <v>5.335802426500619</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2415,22 +2415,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06621883776313559</v>
+        <v>0.06610941316568097</v>
       </c>
       <c r="C15">
-        <v>123.848599190759</v>
+        <v>122.560295412796</v>
       </c>
       <c r="D15">
-        <v>146.519599190759</v>
+        <v>147.1082954127961</v>
       </c>
       <c r="E15">
-        <v>-99.49900000000001</v>
+        <v>-97.622</v>
       </c>
       <c r="F15">
-        <v>24.401</v>
+        <v>26.278</v>
       </c>
       <c r="G15">
         <v>1.73</v>
@@ -2451,28 +2451,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M15">
-        <v>1.3493753</v>
+        <v>1.4531734</v>
       </c>
       <c r="N15">
-        <v>5.850624700000001</v>
+        <v>5.7468266</v>
       </c>
       <c r="O15">
-        <v>1.5504155455</v>
+        <v>1.522909049</v>
       </c>
       <c r="P15">
-        <v>4.300209154500001</v>
+        <v>4.223917551</v>
       </c>
       <c r="Q15">
-        <v>19.9002091545</v>
+        <v>19.823917551</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07004014110705241</v>
+        <v>0.070254701355443</v>
       </c>
       <c r="T15">
-        <v>0.5598185013176076</v>
+        <v>0.5647737033589607</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.335802426500619</v>
+        <v>4.954673681750574</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06610941316568097</v>
+        <v>0.06599998856822636</v>
       </c>
       <c r="C16">
-        <v>122.560295412796</v>
+        <v>121.276741324375</v>
       </c>
       <c r="D16">
-        <v>147.1082954127961</v>
+        <v>147.701741324375</v>
       </c>
       <c r="E16">
-        <v>-97.622</v>
+        <v>-95.745</v>
       </c>
       <c r="F16">
-        <v>26.278</v>
+        <v>28.155</v>
       </c>
       <c r="G16">
         <v>1.73</v>
@@ -2533,28 +2533,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M16">
-        <v>1.4531734</v>
+        <v>1.5569715</v>
       </c>
       <c r="N16">
-        <v>5.7468266</v>
+        <v>5.643028500000001</v>
       </c>
       <c r="O16">
-        <v>1.522909049</v>
+        <v>1.4954025525</v>
       </c>
       <c r="P16">
-        <v>4.223917551</v>
+        <v>4.1476259475</v>
       </c>
       <c r="Q16">
-        <v>19.823917551</v>
+        <v>19.7476259475</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.070254701355443</v>
+        <v>0.07047431008026631</v>
       </c>
       <c r="T16">
-        <v>0.5647737033589607</v>
+        <v>0.5698454983895219</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.954673681750574</v>
+        <v>4.624362102967202</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2579,22 +2579,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06599998856822636</v>
+        <v>0.06618456397077173</v>
       </c>
       <c r="C17">
-        <v>121.276741324375</v>
+        <v>118.401482246391</v>
       </c>
       <c r="D17">
-        <v>147.701741324375</v>
+        <v>146.703482246391</v>
       </c>
       <c r="E17">
-        <v>-95.745</v>
+        <v>-93.86800000000001</v>
       </c>
       <c r="F17">
-        <v>28.155</v>
+        <v>30.032</v>
       </c>
       <c r="G17">
         <v>1.73</v>
@@ -2615,45 +2615,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M17">
-        <v>1.5569715</v>
+        <v>1.7358496</v>
       </c>
       <c r="N17">
-        <v>5.643028500000002</v>
+        <v>5.464150400000001</v>
       </c>
       <c r="O17">
-        <v>1.495402552500001</v>
+        <v>1.447999856</v>
       </c>
       <c r="P17">
-        <v>4.147625947500001</v>
+        <v>4.016150544</v>
       </c>
       <c r="Q17">
-        <v>19.7476259475</v>
+        <v>19.616150544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07047431008026631</v>
+        <v>0.07069914758425207</v>
       </c>
       <c r="T17">
-        <v>0.5698454983895219</v>
+        <v>0.5750380504446205</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.265</v>
       </c>
       <c r="W17">
-        <v>0.0406455</v>
+        <v>0.042483</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.624362102967204</v>
+        <v>4.147824788507023</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2661,22 +2661,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06618456397077173</v>
+        <v>0.06653083937331711</v>
       </c>
       <c r="C18">
-        <v>118.401482246391</v>
+        <v>114.6876316497004</v>
       </c>
       <c r="D18">
-        <v>146.703482246391</v>
+        <v>144.8666316497004</v>
       </c>
       <c r="E18">
-        <v>-93.86800000000001</v>
+        <v>-91.99100000000001</v>
       </c>
       <c r="F18">
-        <v>30.032</v>
+        <v>31.909</v>
       </c>
       <c r="G18">
         <v>1.73</v>
@@ -2697,45 +2697,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M18">
-        <v>1.7358496</v>
+        <v>1.9560217</v>
       </c>
       <c r="N18">
-        <v>5.464150400000001</v>
+        <v>5.243978300000001</v>
       </c>
       <c r="O18">
-        <v>1.447999856</v>
+        <v>1.3896542495</v>
       </c>
       <c r="P18">
-        <v>4.016150544</v>
+        <v>3.854324050500001</v>
       </c>
       <c r="Q18">
-        <v>19.616150544</v>
+        <v>19.4543240505</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07069914758425207</v>
+        <v>0.07092940285941821</v>
       </c>
       <c r="T18">
-        <v>0.5750380504446205</v>
+        <v>0.5803557242359864</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.265</v>
       </c>
       <c r="W18">
-        <v>0.042483</v>
+        <v>0.0450555</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.147824788507023</v>
+        <v>3.680940758479316</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2743,22 +2743,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06653083937331711</v>
+        <v>0.0668359547758625</v>
       </c>
       <c r="C19">
-        <v>114.6876316497004</v>
+        <v>111.2298236516864</v>
       </c>
       <c r="D19">
-        <v>144.8666316497004</v>
+        <v>143.2858236516864</v>
       </c>
       <c r="E19">
-        <v>-91.99100000000001</v>
+        <v>-90.114</v>
       </c>
       <c r="F19">
-        <v>31.909</v>
+        <v>33.786</v>
       </c>
       <c r="G19">
         <v>1.73</v>
@@ -2779,45 +2779,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M19">
-        <v>1.9560217</v>
+        <v>2.1656826</v>
       </c>
       <c r="N19">
-        <v>5.243978300000001</v>
+        <v>5.034317400000001</v>
       </c>
       <c r="O19">
-        <v>1.3896542495</v>
+        <v>1.334094111</v>
       </c>
       <c r="P19">
-        <v>3.854324050500001</v>
+        <v>3.700223289000001</v>
       </c>
       <c r="Q19">
-        <v>19.4543240505</v>
+        <v>19.300223289</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07092940285941821</v>
+        <v>0.07116527411690549</v>
       </c>
       <c r="T19">
-        <v>0.5803557242359864</v>
+        <v>0.5858030973881173</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.265</v>
       </c>
       <c r="W19">
-        <v>0.0450555</v>
+        <v>0.0471135</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.680940758479316</v>
+        <v>3.324586899299094</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2825,22 +2825,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0668359547758625</v>
+        <v>0.06679121017840788</v>
       </c>
       <c r="C20">
-        <v>111.2298236516864</v>
+        <v>109.5824839875684</v>
       </c>
       <c r="D20">
-        <v>143.2858236516864</v>
+        <v>143.5154839875684</v>
       </c>
       <c r="E20">
-        <v>-90.114</v>
+        <v>-88.23700000000001</v>
       </c>
       <c r="F20">
-        <v>33.78599999999999</v>
+        <v>35.663</v>
       </c>
       <c r="G20">
         <v>1.73</v>
@@ -2861,28 +2861,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M20">
-        <v>2.1656826</v>
+        <v>2.2859983</v>
       </c>
       <c r="N20">
-        <v>5.034317400000001</v>
+        <v>4.914001700000001</v>
       </c>
       <c r="O20">
-        <v>1.334094111</v>
+        <v>1.3022104505</v>
       </c>
       <c r="P20">
-        <v>3.700223289000001</v>
+        <v>3.6117912495</v>
       </c>
       <c r="Q20">
-        <v>19.300223289</v>
+        <v>19.2117912495</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07116527411690549</v>
+        <v>0.0714069693560591</v>
       </c>
       <c r="T20">
-        <v>0.5858030973881173</v>
+        <v>0.5913849735810416</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.324586899299095</v>
+        <v>3.149608641441247</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2907,22 +2907,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06679121017840788</v>
+        <v>0.06789306558095326</v>
       </c>
       <c r="C21">
-        <v>109.5824839875684</v>
+        <v>102.2560225342091</v>
       </c>
       <c r="D21">
-        <v>143.5154839875684</v>
+        <v>138.0660225342091</v>
       </c>
       <c r="E21">
-        <v>-88.23700000000001</v>
+        <v>-86.36000000000001</v>
       </c>
       <c r="F21">
-        <v>35.663</v>
+        <v>37.54</v>
       </c>
       <c r="G21">
         <v>1.73</v>
@@ -2943,45 +2943,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M21">
-        <v>2.2859983</v>
+        <v>2.699126</v>
       </c>
       <c r="N21">
-        <v>4.914001700000001</v>
+        <v>4.500874000000001</v>
       </c>
       <c r="O21">
-        <v>1.3022104505</v>
+        <v>1.19273161</v>
       </c>
       <c r="P21">
-        <v>3.6117912495</v>
+        <v>3.308142390000001</v>
       </c>
       <c r="Q21">
-        <v>19.2117912495</v>
+        <v>18.90814239</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0714069693560591</v>
+        <v>0.07165470697619157</v>
       </c>
       <c r="T21">
-        <v>0.5913849735810416</v>
+        <v>0.5971063966787891</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.265</v>
       </c>
       <c r="W21">
-        <v>0.0471135</v>
+        <v>0.0528465</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.149608641441247</v>
+        <v>2.667530156057924</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2989,22 +2989,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06789306558095326</v>
+        <v>0.06790565098349863</v>
       </c>
       <c r="C22">
-        <v>102.2560225342091</v>
+        <v>100.3191681691335</v>
       </c>
       <c r="D22">
-        <v>138.0660225342091</v>
+        <v>138.0061681691335</v>
       </c>
       <c r="E22">
-        <v>-86.36000000000001</v>
+        <v>-84.483</v>
       </c>
       <c r="F22">
-        <v>37.54</v>
+        <v>39.417</v>
       </c>
       <c r="G22">
         <v>1.73</v>
@@ -3025,28 +3025,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M22">
-        <v>2.699126</v>
+        <v>2.8340823</v>
       </c>
       <c r="N22">
-        <v>4.500874000000001</v>
+        <v>4.365917700000001</v>
       </c>
       <c r="O22">
-        <v>1.19273161</v>
+        <v>1.1569681905</v>
       </c>
       <c r="P22">
-        <v>3.308142390000001</v>
+        <v>3.2089495095</v>
       </c>
       <c r="Q22">
-        <v>18.90814239</v>
+        <v>18.8089495095</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07165470697619157</v>
+        <v>0.0719087164348084</v>
       </c>
       <c r="T22">
-        <v>0.5971063966787891</v>
+        <v>0.6029726659309097</v>
       </c>
       <c r="U22">
         <v>0.07190000000000001</v>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>2.667530156057924</v>
+        <v>2.540504910531356</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3071,22 +3071,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06790565098349863</v>
+        <v>0.06854886638604402</v>
       </c>
       <c r="C23">
-        <v>100.3191681691335</v>
+        <v>95.45073363487877</v>
       </c>
       <c r="D23">
-        <v>138.0061681691335</v>
+        <v>135.0147336348788</v>
       </c>
       <c r="E23">
-        <v>-84.483</v>
+        <v>-82.60600000000001</v>
       </c>
       <c r="F23">
-        <v>39.41699999999999</v>
+        <v>41.294</v>
       </c>
       <c r="G23">
         <v>1.73</v>
@@ -3107,45 +3107,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M23">
-        <v>2.8340823</v>
+        <v>3.1300852</v>
       </c>
       <c r="N23">
-        <v>4.365917700000001</v>
+        <v>4.069914800000001</v>
       </c>
       <c r="O23">
-        <v>1.1569681905</v>
+        <v>1.078527422</v>
       </c>
       <c r="P23">
-        <v>3.2089495095</v>
+        <v>2.991387378000001</v>
       </c>
       <c r="Q23">
-        <v>18.8089495095</v>
+        <v>18.591387378</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0719087164348084</v>
+        <v>0.07216923895646668</v>
       </c>
       <c r="T23">
-        <v>0.6029726659309097</v>
+        <v>0.6089893523433412</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.265</v>
       </c>
       <c r="W23">
-        <v>0.0528465</v>
+        <v>0.05571300000000001</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.540504910531356</v>
+        <v>2.300256874796891</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3153,22 +3153,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06854886638604402</v>
+        <v>0.06859011678858939</v>
       </c>
       <c r="C24">
-        <v>95.45073363487877</v>
+        <v>93.38630729597065</v>
       </c>
       <c r="D24">
-        <v>135.0147336348788</v>
+        <v>134.8273072959707</v>
       </c>
       <c r="E24">
-        <v>-82.60600000000001</v>
+        <v>-80.72900000000001</v>
       </c>
       <c r="F24">
-        <v>41.294</v>
+        <v>43.171</v>
       </c>
       <c r="G24">
         <v>1.73</v>
@@ -3189,28 +3189,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M24">
-        <v>3.1300852</v>
+        <v>3.2723618</v>
       </c>
       <c r="N24">
-        <v>4.069914800000001</v>
+        <v>3.927638200000001</v>
       </c>
       <c r="O24">
-        <v>1.078527422</v>
+        <v>1.040824123</v>
       </c>
       <c r="P24">
-        <v>2.991387378000001</v>
+        <v>2.886814077</v>
       </c>
       <c r="Q24">
-        <v>18.591387378</v>
+        <v>18.486814077</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07216923895646668</v>
+        <v>0.07243652829686933</v>
       </c>
       <c r="T24">
-        <v>0.6089893523433412</v>
+        <v>0.6151623163249269</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.300256874796891</v>
+        <v>2.200245706327461</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3235,22 +3235,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06859011678858939</v>
+        <v>0.06863136719113477</v>
       </c>
       <c r="C25">
-        <v>93.38630729597065</v>
+        <v>91.32240060308777</v>
       </c>
       <c r="D25">
-        <v>134.8273072959707</v>
+        <v>134.6404006030878</v>
       </c>
       <c r="E25">
-        <v>-80.72900000000001</v>
+        <v>-78.852</v>
       </c>
       <c r="F25">
-        <v>43.171</v>
+        <v>45.048</v>
       </c>
       <c r="G25">
         <v>1.73</v>
@@ -3271,28 +3271,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M25">
-        <v>3.2723618</v>
+        <v>3.4146384</v>
       </c>
       <c r="N25">
-        <v>3.927638200000001</v>
+        <v>3.785361600000001</v>
       </c>
       <c r="O25">
-        <v>1.040824123</v>
+        <v>1.003120824</v>
       </c>
       <c r="P25">
-        <v>2.886814077</v>
+        <v>2.782240776000001</v>
       </c>
       <c r="Q25">
-        <v>18.486814077</v>
+        <v>18.382240776</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07243652829686933</v>
+        <v>0.07271085156728259</v>
       </c>
       <c r="T25">
-        <v>0.6151623163249269</v>
+        <v>0.6214977267270806</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.200245706327461</v>
+        <v>2.10856880189715</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3317,22 +3317,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06863136719113477</v>
+        <v>0.06867261759368014</v>
       </c>
       <c r="C26">
-        <v>91.32240060308777</v>
+        <v>89.25901139811695</v>
       </c>
       <c r="D26">
-        <v>134.6404006030878</v>
+        <v>134.454011398117</v>
       </c>
       <c r="E26">
-        <v>-78.852</v>
+        <v>-76.97500000000001</v>
       </c>
       <c r="F26">
-        <v>45.04799999999999</v>
+        <v>46.925</v>
       </c>
       <c r="G26">
         <v>1.73</v>
@@ -3353,28 +3353,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M26">
-        <v>3.4146384</v>
+        <v>3.556915</v>
       </c>
       <c r="N26">
-        <v>3.785361600000001</v>
+        <v>3.643085000000001</v>
       </c>
       <c r="O26">
-        <v>1.003120824</v>
+        <v>0.9654175250000003</v>
       </c>
       <c r="P26">
-        <v>2.782240776000001</v>
+        <v>2.677667475000001</v>
       </c>
       <c r="Q26">
-        <v>18.382240776</v>
+        <v>18.277667475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07271085156728259</v>
+        <v>0.07299249012490686</v>
       </c>
       <c r="T26">
-        <v>0.6214977267270806</v>
+        <v>0.6280020814066251</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.10856880189715</v>
+        <v>2.024226049821264</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3399,22 +3399,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06867261759368014</v>
+        <v>0.07142748799622553</v>
       </c>
       <c r="C27">
-        <v>89.25901139811695</v>
+        <v>76.00339201068277</v>
       </c>
       <c r="D27">
-        <v>134.454011398117</v>
+        <v>123.0753920106828</v>
       </c>
       <c r="E27">
-        <v>-76.97500000000001</v>
+        <v>-75.09800000000001</v>
       </c>
       <c r="F27">
-        <v>46.925</v>
+        <v>48.802</v>
       </c>
       <c r="G27">
         <v>1.73</v>
@@ -3435,45 +3435,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M27">
-        <v>3.556915</v>
+        <v>4.39218</v>
       </c>
       <c r="N27">
-        <v>3.643085000000001</v>
+        <v>2.807820000000001</v>
       </c>
       <c r="O27">
-        <v>0.9654175250000003</v>
+        <v>0.7440723000000004</v>
       </c>
       <c r="P27">
-        <v>2.677667475000001</v>
+        <v>2.063747700000001</v>
       </c>
       <c r="Q27">
-        <v>18.277667475</v>
+        <v>17.6637477</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07299249012490686</v>
+        <v>0.0732817405354399</v>
       </c>
       <c r="T27">
-        <v>0.6280020814066251</v>
+        <v>0.6346822294558868</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.265</v>
       </c>
       <c r="W27">
-        <v>0.05571300000000001</v>
+        <v>0.06615</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.024226049821264</v>
+        <v>1.639277078808246</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3481,22 +3481,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07142748799622553</v>
+        <v>0.0715731083987709</v>
       </c>
       <c r="C28">
-        <v>76.00339201068277</v>
+        <v>73.57827957937494</v>
       </c>
       <c r="D28">
-        <v>123.0753920106828</v>
+        <v>122.5272795793749</v>
       </c>
       <c r="E28">
-        <v>-75.09800000000001</v>
+        <v>-73.221</v>
       </c>
       <c r="F28">
-        <v>48.802</v>
+        <v>50.679</v>
       </c>
       <c r="G28">
         <v>1.73</v>
@@ -3517,28 +3517,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M28">
-        <v>4.39218</v>
+        <v>4.56111</v>
       </c>
       <c r="N28">
-        <v>2.807820000000001</v>
+        <v>2.638890000000001</v>
       </c>
       <c r="O28">
-        <v>0.7440723000000004</v>
+        <v>0.6993058500000002</v>
       </c>
       <c r="P28">
-        <v>2.063747700000001</v>
+        <v>1.939584150000001</v>
       </c>
       <c r="Q28">
-        <v>17.6637477</v>
+        <v>17.53958415</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.0732817405354399</v>
+        <v>0.07357891561475466</v>
       </c>
       <c r="T28">
-        <v>0.6346822294558868</v>
+        <v>0.6415453952599228</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3555,7 +3555,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.639277078808246</v>
+        <v>1.578563112926459</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0715731083987709</v>
+        <v>0.07171872880131629</v>
       </c>
       <c r="C29">
-        <v>73.57827957937494</v>
+        <v>71.15802750595302</v>
       </c>
       <c r="D29">
-        <v>122.5272795793749</v>
+        <v>121.984027505953</v>
       </c>
       <c r="E29">
-        <v>-73.221</v>
+        <v>-71.34399999999999</v>
       </c>
       <c r="F29">
-        <v>50.679</v>
+        <v>52.556</v>
       </c>
       <c r="G29">
         <v>1.73</v>
@@ -3599,28 +3599,28 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M29">
-        <v>4.56111</v>
+        <v>4.73004</v>
       </c>
       <c r="N29">
-        <v>2.638890000000001</v>
+        <v>2.469960000000001</v>
       </c>
       <c r="O29">
-        <v>0.6993058500000002</v>
+        <v>0.6545394000000003</v>
       </c>
       <c r="P29">
-        <v>1.939584150000001</v>
+        <v>1.815420600000001</v>
       </c>
       <c r="Q29">
-        <v>17.53958415</v>
+        <v>17.4154206</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07357891561475466</v>
+        <v>0.07388434555738373</v>
       </c>
       <c r="T29">
-        <v>0.6415453952599228</v>
+        <v>0.6485992045585156</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3637,7 +3637,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.578563112926459</v>
+        <v>1.522185858893371</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3645,22 +3645,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07171872880131629</v>
+        <v>0.08525379687658367</v>
       </c>
       <c r="C30">
-        <v>71.15802750595302</v>
+        <v>33.68159238027651</v>
       </c>
       <c r="D30">
-        <v>121.984027505953</v>
+        <v>86.3845923802765</v>
       </c>
       <c r="E30">
-        <v>-71.34399999999999</v>
+        <v>-69.46700000000001</v>
       </c>
       <c r="F30">
-        <v>52.556</v>
+        <v>54.433</v>
       </c>
       <c r="G30">
         <v>1.73</v>
@@ -3681,45 +3681,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M30">
-        <v>4.73004</v>
+        <v>7.990764400000001</v>
       </c>
       <c r="N30">
-        <v>2.469960000000001</v>
+        <v>-0.7907643999999996</v>
       </c>
       <c r="O30">
-        <v>0.6545394000000003</v>
+        <v>-0.2095525659999999</v>
       </c>
       <c r="P30">
-        <v>1.815420600000001</v>
+        <v>-0.5812118339999996</v>
       </c>
       <c r="Q30">
-        <v>17.4154206</v>
+        <v>15.018788166</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07388434555738373</v>
+        <v>0.07443232963700508</v>
       </c>
       <c r="T30">
-        <v>0.6485992045585156</v>
+        <v>0.6612547260278309</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.265</v>
+        <v>0.2387756545544004</v>
       </c>
       <c r="W30">
-        <v>0.06615</v>
+        <v>0.111747733911414</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.522185858893371</v>
+        <v>0.9010402058656617</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3727,22 +3727,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08525379687658366</v>
+        <v>0.08626379687658367</v>
       </c>
       <c r="C31">
-        <v>33.68159238027656</v>
+        <v>29.963476307219</v>
       </c>
       <c r="D31">
-        <v>86.38459238027654</v>
+        <v>84.543476307219</v>
       </c>
       <c r="E31">
-        <v>-69.46700000000001</v>
+        <v>-67.59</v>
       </c>
       <c r="F31">
-        <v>54.43299999999999</v>
+        <v>56.31</v>
       </c>
       <c r="G31">
         <v>1.73</v>
@@ -3763,37 +3763,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M31">
-        <v>7.9907644</v>
+        <v>8.266308</v>
       </c>
       <c r="N31">
-        <v>-0.7907643999999987</v>
+        <v>-1.066307999999999</v>
       </c>
       <c r="O31">
-        <v>-0.2095525659999997</v>
+        <v>-0.2825716199999999</v>
       </c>
       <c r="P31">
-        <v>-0.581211833999999</v>
+        <v>-0.7837363799999995</v>
       </c>
       <c r="Q31">
-        <v>15.018788166</v>
+        <v>14.81626362</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07443232963700508</v>
+        <v>0.07484136291753371</v>
       </c>
       <c r="T31">
-        <v>0.6612547260278309</v>
+        <v>0.6707012221139427</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.2387756545544004</v>
+        <v>0.2308164660692537</v>
       </c>
       <c r="W31">
-        <v>0.111747733911414</v>
+        <v>0.1129161427810336</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9010402058656618</v>
+        <v>0.8710055323368063</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3809,22 +3809,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08626379687658367</v>
+        <v>0.08727379687658367</v>
       </c>
       <c r="C32">
-        <v>29.963476307219</v>
+        <v>26.32220197233269</v>
       </c>
       <c r="D32">
-        <v>84.543476307219</v>
+        <v>82.77920197233269</v>
       </c>
       <c r="E32">
-        <v>-67.59</v>
+        <v>-65.71300000000001</v>
       </c>
       <c r="F32">
-        <v>56.31</v>
+        <v>58.187</v>
       </c>
       <c r="G32">
         <v>1.73</v>
@@ -3845,37 +3845,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M32">
-        <v>8.266308</v>
+        <v>8.541851600000001</v>
       </c>
       <c r="N32">
-        <v>-1.066307999999999</v>
+        <v>-1.3418516</v>
       </c>
       <c r="O32">
-        <v>-0.2825716199999999</v>
+        <v>-0.3555906740000001</v>
       </c>
       <c r="P32">
-        <v>-0.7837363799999995</v>
+        <v>-0.9862609259999999</v>
       </c>
       <c r="Q32">
-        <v>14.81626362</v>
+        <v>14.613739074</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07484136291753371</v>
+        <v>0.07526225223517913</v>
       </c>
       <c r="T32">
-        <v>0.6707012221139427</v>
+        <v>0.6804215296808114</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2308164660692537</v>
+        <v>0.2233707736154068</v>
       </c>
       <c r="W32">
-        <v>0.1129161427810336</v>
+        <v>0.1140091704332583</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8710055323368063</v>
+        <v>0.8429085796807803</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3891,22 +3891,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08727379687658367</v>
+        <v>0.08828379687658368</v>
       </c>
       <c r="C33">
-        <v>26.32220197233269</v>
+        <v>22.75305705584926</v>
       </c>
       <c r="D33">
-        <v>82.77920197233269</v>
+        <v>81.08705705584926</v>
       </c>
       <c r="E33">
-        <v>-65.71300000000001</v>
+        <v>-63.83600000000001</v>
       </c>
       <c r="F33">
-        <v>58.187</v>
+        <v>60.064</v>
       </c>
       <c r="G33">
         <v>1.73</v>
@@ -3927,37 +3927,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M33">
-        <v>8.541851600000001</v>
+        <v>8.8173952</v>
       </c>
       <c r="N33">
-        <v>-1.3418516</v>
+        <v>-1.617395199999999</v>
       </c>
       <c r="O33">
-        <v>-0.3555906740000001</v>
+        <v>-0.4286097279999997</v>
       </c>
       <c r="P33">
-        <v>-0.9862609259999999</v>
+        <v>-1.188785471999999</v>
       </c>
       <c r="Q33">
-        <v>14.613739074</v>
+        <v>14.411214528</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07526225223517913</v>
+        <v>0.07569552065040236</v>
       </c>
       <c r="T33">
-        <v>0.6804215296808114</v>
+        <v>0.6904277286467058</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2233707736154068</v>
+        <v>0.2163904369399254</v>
       </c>
       <c r="W33">
-        <v>0.1140091704332583</v>
+        <v>0.115033883857219</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8429085796807803</v>
+        <v>0.816567686565756</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3973,22 +3973,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08828379687658368</v>
+        <v>0.1075205189300682</v>
       </c>
       <c r="C34">
-        <v>22.75305705584926</v>
+        <v>-1.847162100691122</v>
       </c>
       <c r="D34">
-        <v>81.08705705584926</v>
+        <v>58.36383789930888</v>
       </c>
       <c r="E34">
-        <v>-63.83600000000001</v>
+        <v>-61.959</v>
       </c>
       <c r="F34">
-        <v>60.064</v>
+        <v>61.941</v>
       </c>
       <c r="G34">
         <v>1.73</v>
@@ -4009,45 +4009,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M34">
-        <v>8.8173952</v>
+        <v>12.4377528</v>
       </c>
       <c r="N34">
-        <v>-1.617395199999999</v>
+        <v>-5.237752799999999</v>
       </c>
       <c r="O34">
-        <v>-0.4286097279999997</v>
+        <v>-1.388004492</v>
       </c>
       <c r="P34">
-        <v>-1.188785471999999</v>
+        <v>-3.849748307999999</v>
       </c>
       <c r="Q34">
-        <v>14.411214528</v>
+        <v>11.750251692</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07569552065040236</v>
+        <v>0.0767487702921763</v>
       </c>
       <c r="T34">
-        <v>0.6904277286467058</v>
+        <v>0.7147522007431018</v>
       </c>
       <c r="U34">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.2163904369399254</v>
+        <v>0.1534039171449042</v>
       </c>
       <c r="W34">
-        <v>0.115033883857219</v>
+        <v>0.1699964934373032</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.816567686565756</v>
+        <v>0.5788827062071857</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4055,22 +4055,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1075205189300682</v>
+        <v>0.1090705189300682</v>
       </c>
       <c r="C35">
-        <v>-1.847162100691122</v>
+        <v>-5.012902981051305</v>
       </c>
       <c r="D35">
-        <v>58.36383789930888</v>
+        <v>57.0750970189487</v>
       </c>
       <c r="E35">
-        <v>-61.959</v>
+        <v>-60.08200000000001</v>
       </c>
       <c r="F35">
-        <v>61.941</v>
+        <v>63.818</v>
       </c>
       <c r="G35">
         <v>1.73</v>
@@ -4091,37 +4091,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M35">
-        <v>12.4377528</v>
+        <v>12.8146544</v>
       </c>
       <c r="N35">
-        <v>-5.237752799999999</v>
+        <v>-5.614654399999999</v>
       </c>
       <c r="O35">
-        <v>-1.388004492</v>
+        <v>-1.487883416</v>
       </c>
       <c r="P35">
-        <v>-3.849748307999999</v>
+        <v>-4.126770983999999</v>
       </c>
       <c r="Q35">
-        <v>11.750251692</v>
+        <v>11.473229016</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0767487702921763</v>
+        <v>0.07721769105417897</v>
       </c>
       <c r="T35">
-        <v>0.7147522007431018</v>
+        <v>0.7255817795422397</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1534039171449042</v>
+        <v>0.1488920372288776</v>
       </c>
       <c r="W35">
-        <v>0.1699964934373032</v>
+        <v>0.1709024789244414</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5788827062071857</v>
+        <v>0.5618567442599155</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4137,22 +4137,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1090705189300682</v>
+        <v>0.1106205189300682</v>
       </c>
       <c r="C36">
-        <v>-5.012902981051305</v>
+        <v>-8.122959661643833</v>
       </c>
       <c r="D36">
-        <v>57.0750970189487</v>
+        <v>55.84204033835618</v>
       </c>
       <c r="E36">
-        <v>-60.08200000000001</v>
+        <v>-58.205</v>
       </c>
       <c r="F36">
-        <v>63.818</v>
+        <v>65.69500000000001</v>
       </c>
       <c r="G36">
         <v>1.73</v>
@@ -4173,37 +4173,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M36">
-        <v>12.8146544</v>
+        <v>13.191556</v>
       </c>
       <c r="N36">
-        <v>-5.614654399999999</v>
+        <v>-5.991556000000001</v>
       </c>
       <c r="O36">
-        <v>-1.487883416</v>
+        <v>-1.58776234</v>
       </c>
       <c r="P36">
-        <v>-4.126770983999999</v>
+        <v>-4.403793660000001</v>
       </c>
       <c r="Q36">
-        <v>11.473229016</v>
+        <v>11.19620634</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07721769105417897</v>
+        <v>0.07770104014732018</v>
       </c>
       <c r="T36">
-        <v>0.7255817795422397</v>
+        <v>0.7367445761505818</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1488920372288776</v>
+        <v>0.1446379790223382</v>
       </c>
       <c r="W36">
-        <v>0.1709024789244414</v>
+        <v>0.1717566938123145</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5618567442599155</v>
+        <v>0.5458036944239179</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4219,22 +4219,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1106205189300682</v>
+        <v>0.1121705189300682</v>
       </c>
       <c r="C37">
-        <v>-8.122959661643833</v>
+        <v>-11.18086484433817</v>
       </c>
       <c r="D37">
-        <v>55.84204033835618</v>
+        <v>54.66113515566184</v>
       </c>
       <c r="E37">
-        <v>-58.205</v>
+        <v>-56.328</v>
       </c>
       <c r="F37">
-        <v>65.69500000000001</v>
+        <v>67.572</v>
       </c>
       <c r="G37">
         <v>1.73</v>
@@ -4255,37 +4255,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M37">
-        <v>13.191556</v>
+        <v>13.5684576</v>
       </c>
       <c r="N37">
-        <v>-5.991556000000001</v>
+        <v>-6.368457599999999</v>
       </c>
       <c r="O37">
-        <v>-1.58776234</v>
+        <v>-1.687641264</v>
       </c>
       <c r="P37">
-        <v>-4.403793660000001</v>
+        <v>-4.680816335999999</v>
       </c>
       <c r="Q37">
-        <v>11.19620634</v>
+        <v>10.919183664</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07770104014732018</v>
+        <v>0.07819949389962207</v>
       </c>
       <c r="T37">
-        <v>0.7367445761505818</v>
+        <v>0.7482562101529346</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1446379790223382</v>
+        <v>0.1406202573828289</v>
       </c>
       <c r="W37">
-        <v>0.1717566938123145</v>
+        <v>0.172563452317528</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5458036944239179</v>
+        <v>0.5306424806899201</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4301,22 +4301,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1121705189300682</v>
+        <v>0.1137205189300682</v>
       </c>
       <c r="C38">
-        <v>-11.18086484433817</v>
+        <v>-14.18985859189809</v>
       </c>
       <c r="D38">
-        <v>54.66113515566182</v>
+        <v>53.52914140810191</v>
       </c>
       <c r="E38">
-        <v>-56.32800000000002</v>
+        <v>-54.45100000000001</v>
       </c>
       <c r="F38">
-        <v>67.57199999999999</v>
+        <v>69.449</v>
       </c>
       <c r="G38">
         <v>1.73</v>
@@ -4337,37 +4337,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M38">
-        <v>13.5684576</v>
+        <v>13.9453592</v>
       </c>
       <c r="N38">
-        <v>-6.368457599999997</v>
+        <v>-6.745359199999999</v>
       </c>
       <c r="O38">
-        <v>-1.687641263999999</v>
+        <v>-1.787520188</v>
       </c>
       <c r="P38">
-        <v>-4.680816335999998</v>
+        <v>-4.957839011999999</v>
       </c>
       <c r="Q38">
-        <v>10.919183664</v>
+        <v>10.642160988</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07819949389962207</v>
+        <v>0.07871377158056844</v>
       </c>
       <c r="T38">
-        <v>0.7482562101529345</v>
+        <v>0.7601332928537748</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1406202573828289</v>
+        <v>0.1368197098859956</v>
       </c>
       <c r="W38">
-        <v>0.172563452317528</v>
+        <v>0.1733266022548921</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5306424806899203</v>
+        <v>0.516300792022625</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4383,22 +4383,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1137205189300682</v>
+        <v>0.1152705189300682</v>
       </c>
       <c r="C39">
-        <v>-14.18985859189809</v>
+        <v>-17.15291801493793</v>
       </c>
       <c r="D39">
-        <v>53.52914140810191</v>
+        <v>52.44308198506207</v>
       </c>
       <c r="E39">
-        <v>-54.45100000000001</v>
+        <v>-52.57400000000001</v>
       </c>
       <c r="F39">
-        <v>69.449</v>
+        <v>71.32599999999999</v>
       </c>
       <c r="G39">
         <v>1.73</v>
@@ -4419,37 +4419,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M39">
-        <v>13.9453592</v>
+        <v>14.3222608</v>
       </c>
       <c r="N39">
-        <v>-6.745359199999999</v>
+        <v>-7.122260799999998</v>
       </c>
       <c r="O39">
-        <v>-1.787520188</v>
+        <v>-1.887399112</v>
       </c>
       <c r="P39">
-        <v>-4.957839011999999</v>
+        <v>-5.234861687999998</v>
       </c>
       <c r="Q39">
-        <v>10.642160988</v>
+        <v>10.365138312</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07871377158056844</v>
+        <v>0.079244638864126</v>
       </c>
       <c r="T39">
-        <v>0.7601332928537748</v>
+        <v>0.7723935072546421</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1368197098859956</v>
+        <v>0.1332191912047853</v>
       </c>
       <c r="W39">
-        <v>0.1733266022548921</v>
+        <v>0.1740495864060791</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.516300792022625</v>
+        <v>0.5027139290746613</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4465,22 +4465,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1152705189300682</v>
+        <v>0.1306346361913068</v>
       </c>
       <c r="C40">
-        <v>-17.15291801493793</v>
+        <v>-27.81091278195645</v>
       </c>
       <c r="D40">
-        <v>52.44308198506207</v>
+        <v>43.66208721804355</v>
       </c>
       <c r="E40">
-        <v>-52.57400000000001</v>
+        <v>-50.697</v>
       </c>
       <c r="F40">
-        <v>71.32599999999999</v>
+        <v>73.203</v>
       </c>
       <c r="G40">
         <v>1.73</v>
@@ -4501,45 +4501,45 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M40">
-        <v>14.3222608</v>
+        <v>17.2612674</v>
       </c>
       <c r="N40">
-        <v>-7.122260799999998</v>
+        <v>-10.0612674</v>
       </c>
       <c r="O40">
-        <v>-1.887399112</v>
+        <v>-2.666235861</v>
       </c>
       <c r="P40">
-        <v>-5.234861687999998</v>
+        <v>-7.395031539</v>
       </c>
       <c r="Q40">
-        <v>10.365138312</v>
+        <v>8.204968461</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.079244638864126</v>
+        <v>0.08006195632294547</v>
       </c>
       <c r="T40">
-        <v>0.7723935072546421</v>
+        <v>0.791269199144237</v>
       </c>
       <c r="U40">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1332191912047853</v>
+        <v>0.110536495135925</v>
       </c>
       <c r="W40">
-        <v>0.1740495864060791</v>
+        <v>0.2097354944469489</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.5027139290746613</v>
+        <v>0.4171188495695282</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4547,22 +4547,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1306346361913068</v>
+        <v>0.1325346361913068</v>
       </c>
       <c r="C41">
-        <v>-27.81091278195645</v>
+        <v>-30.57365066028725</v>
       </c>
       <c r="D41">
-        <v>43.66208721804355</v>
+        <v>42.77634933971275</v>
       </c>
       <c r="E41">
-        <v>-50.697</v>
+        <v>-48.82000000000001</v>
       </c>
       <c r="F41">
-        <v>73.203</v>
+        <v>75.08</v>
       </c>
       <c r="G41">
         <v>1.73</v>
@@ -4583,37 +4583,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M41">
-        <v>17.2612674</v>
+        <v>17.703864</v>
       </c>
       <c r="N41">
-        <v>-10.0612674</v>
+        <v>-10.503864</v>
       </c>
       <c r="O41">
-        <v>-2.666235861</v>
+        <v>-2.78352396</v>
       </c>
       <c r="P41">
-        <v>-7.395031539</v>
+        <v>-7.720340039999998</v>
       </c>
       <c r="Q41">
-        <v>8.204968461</v>
+        <v>7.879659960000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08006195632294547</v>
+        <v>0.08063298892832789</v>
       </c>
       <c r="T41">
-        <v>0.791269199144237</v>
+        <v>0.8044570191299744</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.110536495135925</v>
+        <v>0.1077730827575269</v>
       </c>
       <c r="W41">
-        <v>0.2097354944469489</v>
+        <v>0.2103871070857752</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4171188495695282</v>
+        <v>0.4066908783302901</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1325346361913068</v>
+        <v>0.1344346361913068</v>
       </c>
       <c r="C42">
-        <v>-30.57365066028725</v>
+        <v>-33.3011665457413</v>
       </c>
       <c r="D42">
-        <v>42.77634933971275</v>
+        <v>41.92583345425871</v>
       </c>
       <c r="E42">
-        <v>-48.82000000000001</v>
+        <v>-46.943</v>
       </c>
       <c r="F42">
-        <v>75.08</v>
+        <v>76.95700000000001</v>
       </c>
       <c r="G42">
         <v>1.73</v>
@@ -4665,37 +4665,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M42">
-        <v>17.703864</v>
+        <v>18.1464606</v>
       </c>
       <c r="N42">
-        <v>-10.503864</v>
+        <v>-10.9464606</v>
       </c>
       <c r="O42">
-        <v>-2.78352396</v>
+        <v>-2.900812059</v>
       </c>
       <c r="P42">
-        <v>-7.720340039999998</v>
+        <v>-8.045648541</v>
       </c>
       <c r="Q42">
-        <v>7.879659960000001</v>
+        <v>7.554351458999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08063298892832789</v>
+        <v>0.08122337857118089</v>
       </c>
       <c r="T42">
-        <v>0.8044570191299744</v>
+        <v>0.8180918838609909</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.1077730827575269</v>
+        <v>0.105144470982953</v>
       </c>
       <c r="W42">
-        <v>0.2103871070857752</v>
+        <v>0.2110069337422197</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4066908783302901</v>
+        <v>0.396771588614917</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4711,22 +4711,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1344346361913068</v>
+        <v>0.1363346361913068</v>
       </c>
       <c r="C43">
-        <v>-33.3011665457413</v>
+        <v>-35.99552042115056</v>
       </c>
       <c r="D43">
-        <v>41.92583345425871</v>
+        <v>41.10847957884945</v>
       </c>
       <c r="E43">
-        <v>-46.943</v>
+        <v>-45.066</v>
       </c>
       <c r="F43">
-        <v>76.95700000000001</v>
+        <v>78.834</v>
       </c>
       <c r="G43">
         <v>1.73</v>
@@ -4747,37 +4747,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M43">
-        <v>18.1464606</v>
+        <v>18.5890572</v>
       </c>
       <c r="N43">
-        <v>-10.9464606</v>
+        <v>-11.3890572</v>
       </c>
       <c r="O43">
-        <v>-2.900812059</v>
+        <v>-3.018100158000001</v>
       </c>
       <c r="P43">
-        <v>-8.045648541</v>
+        <v>-8.370957042000001</v>
       </c>
       <c r="Q43">
-        <v>7.554351458999999</v>
+        <v>7.229042957999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08122337857118089</v>
+        <v>0.08183412647758057</v>
       </c>
       <c r="T43">
-        <v>0.8180918838609909</v>
+        <v>0.8321969163413527</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.105144470982953</v>
+        <v>0.1026410311976446</v>
       </c>
       <c r="W43">
-        <v>0.2110069337422197</v>
+        <v>0.2115972448435954</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.396771588614917</v>
+        <v>0.3873246460288475</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4793,22 +4793,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1363346361913068</v>
+        <v>0.1382346361913068</v>
       </c>
       <c r="C44">
-        <v>-35.99552042115054</v>
+        <v>-38.6586147017854</v>
       </c>
       <c r="D44">
-        <v>41.10847957884945</v>
+        <v>40.32238529821461</v>
       </c>
       <c r="E44">
-        <v>-45.06600000000002</v>
+        <v>-43.18900000000001</v>
       </c>
       <c r="F44">
-        <v>78.83399999999999</v>
+        <v>80.711</v>
       </c>
       <c r="G44">
         <v>1.73</v>
@@ -4829,37 +4829,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M44">
-        <v>18.5890572</v>
+        <v>19.0316538</v>
       </c>
       <c r="N44">
-        <v>-11.3890572</v>
+        <v>-11.8316538</v>
       </c>
       <c r="O44">
-        <v>-3.018100158</v>
+        <v>-3.135388257</v>
       </c>
       <c r="P44">
-        <v>-8.370957041999999</v>
+        <v>-8.696265542999999</v>
       </c>
       <c r="Q44">
-        <v>7.229042958000001</v>
+        <v>6.903734457000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08183412647758057</v>
+        <v>0.08246630413508199</v>
       </c>
       <c r="T44">
-        <v>0.8321969163413527</v>
+        <v>0.8467968622420782</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1026410311976446</v>
+        <v>0.100254030472118</v>
       </c>
       <c r="W44">
-        <v>0.2115972448435954</v>
+        <v>0.2121600996146746</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3873246460288476</v>
+        <v>0.3783170961212</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4875,22 +4875,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1382346361913068</v>
+        <v>0.1401346361913068</v>
       </c>
       <c r="C45">
-        <v>-38.6586147017854</v>
+        <v>-41.29220901805158</v>
       </c>
       <c r="D45">
-        <v>40.32238529821461</v>
+        <v>39.56579098194842</v>
       </c>
       <c r="E45">
-        <v>-43.18900000000001</v>
+        <v>-41.31200000000001</v>
       </c>
       <c r="F45">
-        <v>80.711</v>
+        <v>82.58799999999999</v>
       </c>
       <c r="G45">
         <v>1.73</v>
@@ -4911,37 +4911,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M45">
-        <v>19.0316538</v>
+        <v>19.4742504</v>
       </c>
       <c r="N45">
-        <v>-11.8316538</v>
+        <v>-12.2742504</v>
       </c>
       <c r="O45">
-        <v>-3.135388257</v>
+        <v>-3.252676356</v>
       </c>
       <c r="P45">
-        <v>-8.696265542999999</v>
+        <v>-9.021574043999998</v>
       </c>
       <c r="Q45">
-        <v>6.903734457000001</v>
+        <v>6.578425956000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08246630413508199</v>
+        <v>0.08312105956606559</v>
       </c>
       <c r="T45">
-        <v>0.8467968622420782</v>
+        <v>0.8619182347821154</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.100254030472118</v>
+        <v>0.09797552977956986</v>
       </c>
       <c r="W45">
-        <v>0.2121600996146746</v>
+        <v>0.2126973700779774</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3783170961212</v>
+        <v>0.3697189803002636</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1401346361913068</v>
+        <v>0.1420346361913068</v>
       </c>
       <c r="C46">
-        <v>-41.29220901805158</v>
+        <v>-43.89793336457763</v>
       </c>
       <c r="D46">
-        <v>39.56579098194842</v>
+        <v>38.83706663542238</v>
       </c>
       <c r="E46">
-        <v>-41.31200000000001</v>
+        <v>-39.435</v>
       </c>
       <c r="F46">
-        <v>82.58799999999999</v>
+        <v>84.465</v>
       </c>
       <c r="G46">
         <v>1.73</v>
@@ -4993,37 +4993,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M46">
-        <v>19.4742504</v>
+        <v>19.916847</v>
       </c>
       <c r="N46">
-        <v>-12.2742504</v>
+        <v>-12.716847</v>
       </c>
       <c r="O46">
-        <v>-3.252676356</v>
+        <v>-3.369964455</v>
       </c>
       <c r="P46">
-        <v>-9.021574043999998</v>
+        <v>-9.346882545</v>
       </c>
       <c r="Q46">
-        <v>6.578425956000002</v>
+        <v>6.253117455</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08312105956606559</v>
+        <v>0.0837996242854486</v>
       </c>
       <c r="T46">
-        <v>0.8619182347821154</v>
+        <v>0.8775894754145175</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09797552977956986</v>
+        <v>0.09579829578446832</v>
       </c>
       <c r="W46">
-        <v>0.2126973700779774</v>
+        <v>0.2132107618540224</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3697189803002636</v>
+        <v>0.3615030029602577</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5039,22 +5039,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1420346361913068</v>
+        <v>0.1439346361913068</v>
       </c>
       <c r="C47">
-        <v>-43.89793336457763</v>
+        <v>-46.47729982249817</v>
       </c>
       <c r="D47">
-        <v>38.83706663542238</v>
+        <v>38.13470017750183</v>
       </c>
       <c r="E47">
-        <v>-39.435</v>
+        <v>-37.55800000000001</v>
       </c>
       <c r="F47">
-        <v>84.465</v>
+        <v>86.342</v>
       </c>
       <c r="G47">
         <v>1.73</v>
@@ -5075,37 +5075,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M47">
-        <v>19.916847</v>
+        <v>20.3594436</v>
       </c>
       <c r="N47">
-        <v>-12.716847</v>
+        <v>-13.1594436</v>
       </c>
       <c r="O47">
-        <v>-3.369964455</v>
+        <v>-3.487252554</v>
       </c>
       <c r="P47">
-        <v>-9.346882545</v>
+        <v>-9.672191046000002</v>
       </c>
       <c r="Q47">
-        <v>6.253117455</v>
+        <v>5.927808953999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0837996242854486</v>
+        <v>0.08450332103147543</v>
       </c>
       <c r="T47">
-        <v>0.8775894754145175</v>
+        <v>0.8938411323666382</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09579829578446832</v>
+        <v>0.09371572413697986</v>
       </c>
       <c r="W47">
-        <v>0.2132107618540224</v>
+        <v>0.2137018322485002</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3615030029602577</v>
+        <v>0.353644242026339</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5121,22 +5121,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1439346361913068</v>
+        <v>0.1458346361913068</v>
       </c>
       <c r="C48">
-        <v>-46.47729982249817</v>
+        <v>-49.03171303235128</v>
       </c>
       <c r="D48">
-        <v>38.13470017750183</v>
+        <v>37.45728696764872</v>
       </c>
       <c r="E48">
-        <v>-37.55800000000001</v>
+        <v>-35.68100000000001</v>
       </c>
       <c r="F48">
-        <v>86.342</v>
+        <v>88.21899999999999</v>
       </c>
       <c r="G48">
         <v>1.73</v>
@@ -5157,37 +5157,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M48">
-        <v>20.3594436</v>
+        <v>20.8020402</v>
       </c>
       <c r="N48">
-        <v>-13.1594436</v>
+        <v>-13.6020402</v>
       </c>
       <c r="O48">
-        <v>-3.487252554</v>
+        <v>-3.604540653</v>
       </c>
       <c r="P48">
-        <v>-9.672191046000002</v>
+        <v>-9.997499547</v>
       </c>
       <c r="Q48">
-        <v>5.927808953999998</v>
+        <v>5.602500452999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08450332103147543</v>
+        <v>0.08523357237169195</v>
       </c>
       <c r="T48">
-        <v>0.8938411323666382</v>
+        <v>0.9107060593924238</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.09371572413697986</v>
+        <v>0.09172177255959732</v>
       </c>
       <c r="W48">
-        <v>0.2137018322485002</v>
+        <v>0.2141720060304469</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.353644242026339</v>
+        <v>0.3461198964513106</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5203,22 +5203,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1458346361913068</v>
+        <v>0.1477346361913068</v>
       </c>
       <c r="C49">
-        <v>-49.03171303235128</v>
+        <v>-51.56247957023356</v>
       </c>
       <c r="D49">
-        <v>37.45728696764872</v>
+        <v>36.80352042976645</v>
       </c>
       <c r="E49">
-        <v>-35.68100000000001</v>
+        <v>-33.804</v>
       </c>
       <c r="F49">
-        <v>88.21899999999999</v>
+        <v>90.096</v>
       </c>
       <c r="G49">
         <v>1.73</v>
@@ -5239,37 +5239,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M49">
-        <v>20.8020402</v>
+        <v>21.2446368</v>
       </c>
       <c r="N49">
-        <v>-13.6020402</v>
+        <v>-14.0446368</v>
       </c>
       <c r="O49">
-        <v>-3.604540653</v>
+        <v>-3.721828752</v>
       </c>
       <c r="P49">
-        <v>-9.997499547</v>
+        <v>-10.322808048</v>
       </c>
       <c r="Q49">
-        <v>5.602500452999999</v>
+        <v>5.277191951999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08523357237169195</v>
+        <v>0.0859919103019168</v>
       </c>
       <c r="T49">
-        <v>0.9107060593924238</v>
+        <v>0.9282196374576628</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.09172177255959732</v>
+        <v>0.08981090229793903</v>
       </c>
       <c r="W49">
-        <v>0.2141720060304469</v>
+        <v>0.214622589238146</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3461198964513106</v>
+        <v>0.3389090652752417</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5285,22 +5285,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1477346361913068</v>
+        <v>0.1496346361913068</v>
       </c>
       <c r="C50">
-        <v>-51.56247957023354</v>
+        <v>-54.0708163589097</v>
       </c>
       <c r="D50">
-        <v>36.80352042976645</v>
+        <v>36.1721836410903</v>
       </c>
       <c r="E50">
-        <v>-33.80400000000002</v>
+        <v>-31.92700000000001</v>
       </c>
       <c r="F50">
-        <v>90.09599999999999</v>
+        <v>91.973</v>
       </c>
       <c r="G50">
         <v>1.73</v>
@@ -5321,37 +5321,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M50">
-        <v>21.2446368</v>
+        <v>21.6872334</v>
       </c>
       <c r="N50">
-        <v>-14.0446368</v>
+        <v>-14.4872334</v>
       </c>
       <c r="O50">
-        <v>-3.721828752</v>
+        <v>-3.839116851</v>
       </c>
       <c r="P50">
-        <v>-10.322808048</v>
+        <v>-10.648116549</v>
       </c>
       <c r="Q50">
-        <v>5.277191952000001</v>
+        <v>4.951883451</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0859919103019168</v>
+        <v>0.0867799869745034</v>
       </c>
       <c r="T50">
-        <v>0.9282196374576627</v>
+        <v>0.9464200225058522</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08981090229793905</v>
+        <v>0.08797802674083824</v>
       </c>
       <c r="W50">
-        <v>0.214622589238146</v>
+        <v>0.2150547812945104</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3389090652752417</v>
+        <v>0.3319925537390123</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5367,22 +5367,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1496346361913068</v>
+        <v>0.1515346361913068</v>
       </c>
       <c r="C51">
-        <v>-54.0708163589097</v>
+        <v>-56.55785822780508</v>
       </c>
       <c r="D51">
-        <v>36.1721836410903</v>
+        <v>35.56214177219491</v>
       </c>
       <c r="E51">
-        <v>-31.92700000000001</v>
+        <v>-30.05000000000001</v>
       </c>
       <c r="F51">
-        <v>91.973</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="G51">
         <v>1.73</v>
@@ -5403,37 +5403,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M51">
-        <v>21.6872334</v>
+        <v>22.12983</v>
       </c>
       <c r="N51">
-        <v>-14.4872334</v>
+        <v>-14.92983</v>
       </c>
       <c r="O51">
-        <v>-3.839116851</v>
+        <v>-3.95640495</v>
       </c>
       <c r="P51">
-        <v>-10.648116549</v>
+        <v>-10.97342505</v>
       </c>
       <c r="Q51">
-        <v>4.951883451</v>
+        <v>4.626574950000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.0867799869745034</v>
+        <v>0.08759958671399347</v>
       </c>
       <c r="T51">
-        <v>0.9464200225058522</v>
+        <v>0.9653484229559692</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08797802674083824</v>
+        <v>0.08621846620602149</v>
       </c>
       <c r="W51">
-        <v>0.2150547812945104</v>
+        <v>0.2154696856686202</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3319925537390123</v>
+        <v>0.325352702664232</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5449,22 +5449,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1515346361913068</v>
+        <v>0.1534346361913068</v>
       </c>
       <c r="C52">
-        <v>-56.55785822780508</v>
+        <v>-59.0246647206923</v>
       </c>
       <c r="D52">
-        <v>35.56214177219491</v>
+        <v>34.97233527930769</v>
       </c>
       <c r="E52">
-        <v>-30.05000000000001</v>
+        <v>-28.17300000000002</v>
       </c>
       <c r="F52">
-        <v>93.84999999999999</v>
+        <v>95.72699999999999</v>
       </c>
       <c r="G52">
         <v>1.73</v>
@@ -5485,37 +5485,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M52">
-        <v>22.12983</v>
+        <v>22.5724266</v>
       </c>
       <c r="N52">
-        <v>-14.92983</v>
+        <v>-15.3724266</v>
       </c>
       <c r="O52">
-        <v>-3.95640495</v>
+        <v>-4.073693049</v>
       </c>
       <c r="P52">
-        <v>-10.97342505</v>
+        <v>-11.298733551</v>
       </c>
       <c r="Q52">
-        <v>4.626574950000002</v>
+        <v>4.301266449000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08759958671399347</v>
+        <v>0.08845263950407496</v>
       </c>
       <c r="T52">
-        <v>0.9653484229559692</v>
+        <v>0.9850494111795604</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08621846620602149</v>
+        <v>0.0845279080451191</v>
       </c>
       <c r="W52">
-        <v>0.2154696856686202</v>
+        <v>0.2158683192829609</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.325352702664232</v>
+        <v>0.3189732379061098</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5531,22 +5531,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1534346361913068</v>
+        <v>0.1553346361913068</v>
       </c>
       <c r="C53">
-        <v>-59.0246647206923</v>
+        <v>-61.47222623698791</v>
       </c>
       <c r="D53">
-        <v>34.97233527930769</v>
+        <v>34.40177376301209</v>
       </c>
       <c r="E53">
-        <v>-28.17300000000002</v>
+        <v>-26.29600000000001</v>
       </c>
       <c r="F53">
-        <v>95.72699999999999</v>
+        <v>97.604</v>
       </c>
       <c r="G53">
         <v>1.73</v>
@@ -5567,37 +5567,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M53">
-        <v>22.5724266</v>
+        <v>23.0150232</v>
       </c>
       <c r="N53">
-        <v>-15.3724266</v>
+        <v>-15.8150232</v>
       </c>
       <c r="O53">
-        <v>-4.073693049</v>
+        <v>-4.190981148000001</v>
       </c>
       <c r="P53">
-        <v>-11.298733551</v>
+        <v>-11.624042052</v>
       </c>
       <c r="Q53">
-        <v>4.301266449000002</v>
+        <v>3.975957948</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08845263950407496</v>
+        <v>0.08934123616040987</v>
       </c>
       <c r="T53">
-        <v>0.9850494111795604</v>
+        <v>1.005571273912468</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.0845279080451191</v>
+        <v>0.08290237135194373</v>
       </c>
       <c r="W53">
-        <v>0.2158683192829609</v>
+        <v>0.2162516208352117</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3189732379061098</v>
+        <v>0.3128391371771462</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5613,22 +5613,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1553346361913068</v>
+        <v>0.1572346361913068</v>
       </c>
       <c r="C54">
-        <v>-61.47222623698791</v>
+        <v>-63.90146958154023</v>
       </c>
       <c r="D54">
-        <v>34.40177376301209</v>
+        <v>33.84953041845977</v>
       </c>
       <c r="E54">
-        <v>-26.29600000000001</v>
+        <v>-24.41900000000001</v>
       </c>
       <c r="F54">
-        <v>97.604</v>
+        <v>99.48099999999999</v>
       </c>
       <c r="G54">
         <v>1.73</v>
@@ -5649,37 +5649,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M54">
-        <v>23.0150232</v>
+        <v>23.4576198</v>
       </c>
       <c r="N54">
-        <v>-15.8150232</v>
+        <v>-16.2576198</v>
       </c>
       <c r="O54">
-        <v>-4.190981148000001</v>
+        <v>-4.308269247</v>
       </c>
       <c r="P54">
-        <v>-11.624042052</v>
+        <v>-11.949350553</v>
       </c>
       <c r="Q54">
-        <v>3.975957948</v>
+        <v>3.650649446999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08934123616040987</v>
+        <v>0.09026764544041857</v>
       </c>
       <c r="T54">
-        <v>1.005571273912468</v>
+        <v>1.026966407399967</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.08290237135194373</v>
+        <v>0.08133817566605801</v>
       </c>
       <c r="W54">
-        <v>0.2162516208352117</v>
+        <v>0.2166204581779435</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3128391371771462</v>
+        <v>0.3069365119473886</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1572346361913068</v>
+        <v>0.1591346361913068</v>
       </c>
       <c r="C55">
-        <v>-63.90146958154023</v>
+        <v>-66.31326298832639</v>
       </c>
       <c r="D55">
-        <v>33.84953041845977</v>
+        <v>33.31473701167361</v>
       </c>
       <c r="E55">
-        <v>-24.41900000000001</v>
+        <v>-22.542</v>
       </c>
       <c r="F55">
-        <v>99.48099999999999</v>
+        <v>101.358</v>
       </c>
       <c r="G55">
         <v>1.73</v>
@@ -5731,37 +5731,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M55">
-        <v>23.4576198</v>
+        <v>23.9002164</v>
       </c>
       <c r="N55">
-        <v>-16.2576198</v>
+        <v>-16.7002164</v>
       </c>
       <c r="O55">
-        <v>-4.308269247</v>
+        <v>-4.425557346000001</v>
       </c>
       <c r="P55">
-        <v>-11.949350553</v>
+        <v>-12.274659054</v>
       </c>
       <c r="Q55">
-        <v>3.650649446999999</v>
+        <v>3.325340945999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09026764544041857</v>
+        <v>0.0912343333847755</v>
       </c>
       <c r="T55">
-        <v>1.026966407399967</v>
+        <v>1.049291764082575</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.08133817566605801</v>
+        <v>0.07983191315372359</v>
       </c>
       <c r="W55">
-        <v>0.2166204581779435</v>
+        <v>0.216975634878352</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3069365119473886</v>
+        <v>0.3012525024668814</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5777,22 +5777,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1591346361913068</v>
+        <v>0.1610346361913068</v>
       </c>
       <c r="C56">
-        <v>-66.31326298832639</v>
+        <v>-68.70842067533539</v>
       </c>
       <c r="D56">
-        <v>33.31473701167361</v>
+        <v>32.79657932466461</v>
       </c>
       <c r="E56">
-        <v>-22.542</v>
+        <v>-20.66500000000001</v>
       </c>
       <c r="F56">
-        <v>101.358</v>
+        <v>103.235</v>
       </c>
       <c r="G56">
         <v>1.73</v>
@@ -5813,37 +5813,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M56">
-        <v>23.9002164</v>
+        <v>24.342813</v>
       </c>
       <c r="N56">
-        <v>-16.7002164</v>
+        <v>-17.142813</v>
       </c>
       <c r="O56">
-        <v>-4.425557346000001</v>
+        <v>-4.542845444999999</v>
       </c>
       <c r="P56">
-        <v>-12.274659054</v>
+        <v>-12.599967555</v>
       </c>
       <c r="Q56">
-        <v>3.325340945999999</v>
+        <v>3.000032445000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.0912343333847755</v>
+        <v>0.09224398523777053</v>
       </c>
       <c r="T56">
-        <v>1.049291764082575</v>
+        <v>1.072609358839966</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07983191315372359</v>
+        <v>0.0783804238236559</v>
       </c>
       <c r="W56">
-        <v>0.216975634878352</v>
+        <v>0.217317896062382</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3012525024668814</v>
+        <v>0.295775184240211</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5859,22 +5859,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1610346361913068</v>
+        <v>0.1629346361913068</v>
       </c>
       <c r="C57">
-        <v>-68.70842067533539</v>
+        <v>-71.08770698089756</v>
       </c>
       <c r="D57">
-        <v>32.79657932466461</v>
+        <v>32.29429301910244</v>
       </c>
       <c r="E57">
-        <v>-20.66500000000001</v>
+        <v>-18.788</v>
       </c>
       <c r="F57">
-        <v>103.235</v>
+        <v>105.112</v>
       </c>
       <c r="G57">
         <v>1.73</v>
@@ -5895,37 +5895,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M57">
-        <v>24.342813</v>
+        <v>24.7854096</v>
       </c>
       <c r="N57">
-        <v>-17.142813</v>
+        <v>-17.58540960000001</v>
       </c>
       <c r="O57">
-        <v>-4.542845444999999</v>
+        <v>-4.660133544000002</v>
       </c>
       <c r="P57">
-        <v>-12.599967555</v>
+        <v>-12.925276056</v>
       </c>
       <c r="Q57">
-        <v>3.000032445000002</v>
+        <v>2.674723943999995</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09224398523777053</v>
+        <v>0.09329953035681077</v>
       </c>
       <c r="T57">
-        <v>1.072609358839966</v>
+        <v>1.096986844268147</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.0783804238236559</v>
+        <v>0.07698077339823345</v>
       </c>
       <c r="W57">
-        <v>0.217317896062382</v>
+        <v>0.2176479336326965</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.295775184240211</v>
+        <v>0.2904934845216356</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5941,22 +5941,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1629346361913068</v>
+        <v>0.1648346361913068</v>
       </c>
       <c r="C58">
-        <v>-71.08770698089756</v>
+        <v>-73.45184012565498</v>
       </c>
       <c r="D58">
-        <v>32.29429301910244</v>
+        <v>31.80715987434503</v>
       </c>
       <c r="E58">
-        <v>-18.788</v>
+        <v>-16.911</v>
       </c>
       <c r="F58">
-        <v>105.112</v>
+        <v>106.989</v>
       </c>
       <c r="G58">
         <v>1.73</v>
@@ -5977,37 +5977,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M58">
-        <v>24.7854096</v>
+        <v>25.2280062</v>
       </c>
       <c r="N58">
-        <v>-17.58540960000001</v>
+        <v>-18.0280062</v>
       </c>
       <c r="O58">
-        <v>-4.660133544000002</v>
+        <v>-4.777421643</v>
       </c>
       <c r="P58">
-        <v>-12.925276056</v>
+        <v>-13.250584557</v>
       </c>
       <c r="Q58">
-        <v>2.674723943999995</v>
+        <v>2.349415443</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09329953035681077</v>
+        <v>0.09440417059766681</v>
       </c>
       <c r="T58">
-        <v>1.096986844268147</v>
+        <v>1.122498166227871</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07698077339823345</v>
+        <v>0.07563023351405393</v>
       </c>
       <c r="W58">
-        <v>0.2176479336326965</v>
+        <v>0.2179663909373861</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2904934845216356</v>
+        <v>0.2853971076002035</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6023,22 +6023,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1648346361913068</v>
+        <v>0.1667346361913068</v>
       </c>
       <c r="C59">
-        <v>-73.45184012565498</v>
+        <v>-75.8014956391138</v>
       </c>
       <c r="D59">
-        <v>31.80715987434503</v>
+        <v>31.3345043608862</v>
       </c>
       <c r="E59">
-        <v>-16.911</v>
+        <v>-15.03400000000001</v>
       </c>
       <c r="F59">
-        <v>106.989</v>
+        <v>108.866</v>
       </c>
       <c r="G59">
         <v>1.73</v>
@@ -6059,37 +6059,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M59">
-        <v>25.2280062</v>
+        <v>25.6706028</v>
       </c>
       <c r="N59">
-        <v>-18.0280062</v>
+        <v>-18.4706028</v>
       </c>
       <c r="O59">
-        <v>-4.777421643</v>
+        <v>-4.894709742000001</v>
       </c>
       <c r="P59">
-        <v>-13.250584557</v>
+        <v>-13.575893058</v>
       </c>
       <c r="Q59">
-        <v>2.349415443</v>
+        <v>2.024106941999998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09440417059766681</v>
+        <v>0.09556141275475413</v>
       </c>
       <c r="T59">
-        <v>1.122498166227871</v>
+        <v>1.149224313042821</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07563023351405393</v>
+        <v>0.07432626397070817</v>
       </c>
       <c r="W59">
-        <v>0.2179663909373861</v>
+        <v>0.218273866955707</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2853971076002035</v>
+        <v>0.280476467813993</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6105,22 +6105,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1667346361913068</v>
+        <v>0.1686346361913068</v>
       </c>
       <c r="C60">
-        <v>-75.80149563911378</v>
+        <v>-78.1373094851579</v>
       </c>
       <c r="D60">
-        <v>31.3345043608862</v>
+        <v>30.87569051484208</v>
       </c>
       <c r="E60">
-        <v>-15.03400000000002</v>
+        <v>-13.15700000000002</v>
       </c>
       <c r="F60">
-        <v>108.866</v>
+        <v>110.743</v>
       </c>
       <c r="G60">
         <v>1.73</v>
@@ -6141,37 +6141,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M60">
-        <v>25.6706028</v>
+        <v>26.1131994</v>
       </c>
       <c r="N60">
-        <v>-18.47060279999999</v>
+        <v>-18.9131994</v>
       </c>
       <c r="O60">
-        <v>-4.894709741999999</v>
+        <v>-5.011997840999999</v>
       </c>
       <c r="P60">
-        <v>-13.57589305799999</v>
+        <v>-13.901201559</v>
       </c>
       <c r="Q60">
-        <v>2.024106942000005</v>
+        <v>1.698798441000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.0955614127547541</v>
+        <v>0.09677510574877252</v>
       </c>
       <c r="T60">
-        <v>1.14922431304282</v>
+        <v>1.177254174336548</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07432626397070817</v>
+        <v>0.07306649678476398</v>
       </c>
       <c r="W60">
-        <v>0.218273866955707</v>
+        <v>0.2185709200581527</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2804764678139932</v>
+        <v>0.2757226293764677</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6187,22 +6187,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1686346361913068</v>
+        <v>0.1705346361913068</v>
       </c>
       <c r="C61">
-        <v>-78.1373094851579</v>
+        <v>-80.45988091693425</v>
       </c>
       <c r="D61">
-        <v>30.87569051484208</v>
+        <v>30.43011908306574</v>
       </c>
       <c r="E61">
-        <v>-13.15700000000002</v>
+        <v>-11.28000000000002</v>
       </c>
       <c r="F61">
-        <v>110.743</v>
+        <v>112.62</v>
       </c>
       <c r="G61">
         <v>1.73</v>
@@ -6223,37 +6223,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M61">
-        <v>26.1131994</v>
+        <v>26.555796</v>
       </c>
       <c r="N61">
-        <v>-18.9131994</v>
+        <v>-19.355796</v>
       </c>
       <c r="O61">
-        <v>-5.011997840999999</v>
+        <v>-5.12928594</v>
       </c>
       <c r="P61">
-        <v>-13.901201559</v>
+        <v>-14.22651006</v>
       </c>
       <c r="Q61">
-        <v>1.698798441000003</v>
+        <v>1.373489940000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09677510574877252</v>
+        <v>0.09804948339249182</v>
       </c>
       <c r="T61">
-        <v>1.177254174336548</v>
+        <v>1.206685528694961</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07306649678476398</v>
+        <v>0.07184872183835124</v>
       </c>
       <c r="W61">
-        <v>0.2185709200581527</v>
+        <v>0.2188580713905168</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2757226293764677</v>
+        <v>0.2711272522201933</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6269,22 +6269,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1705346361913068</v>
+        <v>0.1724346361913068</v>
       </c>
       <c r="C62">
-        <v>-80.45988091693425</v>
+        <v>-82.76977508805909</v>
       </c>
       <c r="D62">
-        <v>30.43011908306574</v>
+        <v>29.99722491194089</v>
       </c>
       <c r="E62">
-        <v>-11.28000000000002</v>
+        <v>-9.40300000000002</v>
       </c>
       <c r="F62">
-        <v>112.62</v>
+        <v>114.497</v>
       </c>
       <c r="G62">
         <v>1.73</v>
@@ -6305,37 +6305,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M62">
-        <v>26.555796</v>
+        <v>26.9983926</v>
       </c>
       <c r="N62">
-        <v>-19.355796</v>
+        <v>-19.7983926</v>
       </c>
       <c r="O62">
-        <v>-5.12928594</v>
+        <v>-5.246574039</v>
       </c>
       <c r="P62">
-        <v>-14.22651006</v>
+        <v>-14.551818561</v>
       </c>
       <c r="Q62">
-        <v>1.373489940000001</v>
+        <v>1.048181439</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09804948339249182</v>
+        <v>0.09938921373588905</v>
       </c>
       <c r="T62">
-        <v>1.206685528694961</v>
+        <v>1.237626183276884</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07184872183835124</v>
+        <v>0.07067087393936188</v>
       </c>
       <c r="W62">
-        <v>0.2188580713905168</v>
+        <v>0.2191358079250985</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2711272522201933</v>
+        <v>0.2666825431674033</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6351,22 +6351,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1724346361913068</v>
+        <v>0.1743346361913068</v>
       </c>
       <c r="C63">
-        <v>-82.76977508805909</v>
+        <v>-85.06752544407101</v>
       </c>
       <c r="D63">
-        <v>29.99722491194089</v>
+        <v>29.57647455592898</v>
       </c>
       <c r="E63">
-        <v>-9.40300000000002</v>
+        <v>-7.52600000000001</v>
       </c>
       <c r="F63">
-        <v>114.497</v>
+        <v>116.374</v>
       </c>
       <c r="G63">
         <v>1.73</v>
@@ -6387,37 +6387,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M63">
-        <v>26.9983926</v>
+        <v>27.4409892</v>
       </c>
       <c r="N63">
-        <v>-19.7983926</v>
+        <v>-20.2409892</v>
       </c>
       <c r="O63">
-        <v>-5.246574039</v>
+        <v>-5.363862138000001</v>
       </c>
       <c r="P63">
-        <v>-14.551818561</v>
+        <v>-14.877127062</v>
       </c>
       <c r="Q63">
-        <v>1.048181439</v>
+        <v>0.7228729380000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09938921373588905</v>
+        <v>0.100799456202623</v>
       </c>
       <c r="T63">
-        <v>1.237626183276884</v>
+        <v>1.270195293363117</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07067087393936188</v>
+        <v>0.0695310211338883</v>
       </c>
       <c r="W63">
-        <v>0.2191358079250985</v>
+        <v>0.2194045852166291</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2666825431674033</v>
+        <v>0.2623812118259935</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6433,22 +6433,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1743346361913068</v>
+        <v>0.1762346361913068</v>
       </c>
       <c r="C64">
-        <v>-85.06752544407101</v>
+        <v>-87.35363591540782</v>
       </c>
       <c r="D64">
-        <v>29.57647455592898</v>
+        <v>29.16736408459217</v>
       </c>
       <c r="E64">
-        <v>-7.52600000000001</v>
+        <v>-5.649000000000015</v>
       </c>
       <c r="F64">
-        <v>116.374</v>
+        <v>118.251</v>
       </c>
       <c r="G64">
         <v>1.73</v>
@@ -6469,37 +6469,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M64">
-        <v>27.4409892</v>
+        <v>27.8835858</v>
       </c>
       <c r="N64">
-        <v>-20.2409892</v>
+        <v>-20.6835858</v>
       </c>
       <c r="O64">
-        <v>-5.363862138000001</v>
+        <v>-5.481150237</v>
       </c>
       <c r="P64">
-        <v>-14.877127062</v>
+        <v>-15.202435563</v>
       </c>
       <c r="Q64">
-        <v>0.7228729380000001</v>
+        <v>0.3975644370000033</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.100799456202623</v>
+        <v>0.1022859279918831</v>
       </c>
       <c r="T64">
-        <v>1.270195293363117</v>
+        <v>1.304524895886445</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0695310211338883</v>
+        <v>0.06842735413176308</v>
       </c>
       <c r="W64">
-        <v>0.2194045852166291</v>
+        <v>0.2196648298957303</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2623812118259935</v>
+        <v>0.2582164306858985</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6515,22 +6515,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1762346361913068</v>
+        <v>0.1781346361913068</v>
       </c>
       <c r="C65">
-        <v>-87.35363591540782</v>
+        <v>-89.62858293086376</v>
       </c>
       <c r="D65">
-        <v>29.16736408459217</v>
+        <v>28.76941706913624</v>
       </c>
       <c r="E65">
-        <v>-5.649000000000015</v>
+        <v>-3.772000000000006</v>
       </c>
       <c r="F65">
-        <v>118.251</v>
+        <v>120.128</v>
       </c>
       <c r="G65">
         <v>1.73</v>
@@ -6551,37 +6551,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M65">
-        <v>27.8835858</v>
+        <v>28.3261824</v>
       </c>
       <c r="N65">
-        <v>-20.6835858</v>
+        <v>-21.1261824</v>
       </c>
       <c r="O65">
-        <v>-5.481150237</v>
+        <v>-5.598438336</v>
       </c>
       <c r="P65">
-        <v>-15.202435563</v>
+        <v>-15.527744064</v>
       </c>
       <c r="Q65">
-        <v>0.3975644370000033</v>
+        <v>0.07225593600000302</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1022859279918831</v>
+        <v>0.1038549815472131</v>
       </c>
       <c r="T65">
-        <v>1.304524895886445</v>
+        <v>1.340761698549957</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06842735413176308</v>
+        <v>0.06735817672345427</v>
       </c>
       <c r="W65">
-        <v>0.2196648298957303</v>
+        <v>0.2199169419286095</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2582164306858985</v>
+        <v>0.2541817989564313</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6597,22 +6597,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1781346361913068</v>
+        <v>0.1800346361913068</v>
       </c>
       <c r="C66">
-        <v>-89.62858293086376</v>
+        <v>-91.89281726844024</v>
       </c>
       <c r="D66">
-        <v>28.76941706913624</v>
+        <v>28.38218273155976</v>
       </c>
       <c r="E66">
-        <v>-3.772000000000006</v>
+        <v>-1.89500000000001</v>
       </c>
       <c r="F66">
-        <v>120.128</v>
+        <v>122.005</v>
       </c>
       <c r="G66">
         <v>1.73</v>
@@ -6633,37 +6633,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M66">
-        <v>28.3261824</v>
+        <v>28.768779</v>
       </c>
       <c r="N66">
-        <v>-21.1261824</v>
+        <v>-21.568779</v>
       </c>
       <c r="O66">
-        <v>-5.598438336</v>
+        <v>-5.715726435</v>
       </c>
       <c r="P66">
-        <v>-15.527744064</v>
+        <v>-15.853052565</v>
       </c>
       <c r="Q66">
-        <v>0.07225593600000302</v>
+        <v>-0.2530525649999991</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1038549815472131</v>
+        <v>0.105513695305705</v>
       </c>
       <c r="T66">
-        <v>1.340761698549957</v>
+        <v>1.379069175651385</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06735817672345427</v>
+        <v>0.06632189708155499</v>
       </c>
       <c r="W66">
-        <v>0.2199169419286095</v>
+        <v>0.2201612966681693</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2541817989564313</v>
+        <v>0.2502713097417169</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6679,22 +6679,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1800346361913068</v>
+        <v>0.1819346361913068</v>
       </c>
       <c r="C67">
-        <v>-91.89281726844024</v>
+        <v>-94.14676575870821</v>
       </c>
       <c r="D67">
-        <v>28.38218273155976</v>
+        <v>28.00523424129179</v>
       </c>
       <c r="E67">
-        <v>-1.89500000000001</v>
+        <v>-0.01800000000000068</v>
       </c>
       <c r="F67">
-        <v>122.005</v>
+        <v>123.882</v>
       </c>
       <c r="G67">
         <v>1.73</v>
@@ -6715,37 +6715,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M67">
-        <v>28.768779</v>
+        <v>29.2113756</v>
       </c>
       <c r="N67">
-        <v>-21.568779</v>
+        <v>-22.0113756</v>
       </c>
       <c r="O67">
-        <v>-5.715726435</v>
+        <v>-5.833014534</v>
       </c>
       <c r="P67">
-        <v>-15.853052565</v>
+        <v>-16.178361066</v>
       </c>
       <c r="Q67">
-        <v>-0.2530525649999991</v>
+        <v>-0.5783610660000011</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.105513695305705</v>
+        <v>0.1072699804617551</v>
       </c>
       <c r="T67">
-        <v>1.379069175651385</v>
+        <v>1.419630033758778</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06632189708155499</v>
+        <v>0.06531701985304657</v>
       </c>
       <c r="W67">
-        <v>0.2201612966681693</v>
+        <v>0.2203982467186516</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6753,7 +6753,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2502713097417169</v>
+        <v>0.2464793202001758</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1819346361913068</v>
+        <v>0.1838346361913068</v>
       </c>
       <c r="C68">
-        <v>-94.14676575870821</v>
+        <v>-96.39083285421364</v>
       </c>
       <c r="D68">
-        <v>28.00523424129179</v>
+        <v>27.63816714578636</v>
       </c>
       <c r="E68">
-        <v>-0.01800000000000068</v>
+        <v>1.858999999999995</v>
       </c>
       <c r="F68">
-        <v>123.882</v>
+        <v>125.759</v>
       </c>
       <c r="G68">
         <v>1.73</v>
@@ -6797,37 +6797,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M68">
-        <v>29.2113756</v>
+        <v>29.6539722</v>
       </c>
       <c r="N68">
-        <v>-22.0113756</v>
+        <v>-22.4539722</v>
       </c>
       <c r="O68">
-        <v>-5.833014534</v>
+        <v>-5.950302633000001</v>
       </c>
       <c r="P68">
-        <v>-16.178361066</v>
+        <v>-16.503669567</v>
       </c>
       <c r="Q68">
-        <v>-0.5783610660000011</v>
+        <v>-0.9036695670000032</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1072699804617551</v>
+        <v>0.1091327071424144</v>
       </c>
       <c r="T68">
-        <v>1.419630033758778</v>
+        <v>1.462649125690863</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06531701985304657</v>
+        <v>0.06434213895971752</v>
       </c>
       <c r="W68">
-        <v>0.2203982467186516</v>
+        <v>0.2206281236332986</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2464793202001758</v>
+        <v>0.2428005243762924</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6843,22 +6843,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1838346361913068</v>
+        <v>0.1857346361913068</v>
       </c>
       <c r="C69">
-        <v>-96.39083285421364</v>
+        <v>-98.62540207705773</v>
       </c>
       <c r="D69">
-        <v>27.63816714578636</v>
+        <v>27.28059792294227</v>
       </c>
       <c r="E69">
-        <v>1.858999999999995</v>
+        <v>3.73599999999999</v>
       </c>
       <c r="F69">
-        <v>125.759</v>
+        <v>127.636</v>
       </c>
       <c r="G69">
         <v>1.73</v>
@@ -6879,37 +6879,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M69">
-        <v>29.6539722</v>
+        <v>30.0965688</v>
       </c>
       <c r="N69">
-        <v>-22.4539722</v>
+        <v>-22.8965688</v>
       </c>
       <c r="O69">
-        <v>-5.950302633000001</v>
+        <v>-6.067590731999999</v>
       </c>
       <c r="P69">
-        <v>-16.503669567</v>
+        <v>-16.828978068</v>
       </c>
       <c r="Q69">
-        <v>-0.9036695670000032</v>
+        <v>-1.228978067999998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1091327071424144</v>
+        <v>0.1111118542406148</v>
       </c>
       <c r="T69">
-        <v>1.462649125690863</v>
+        <v>1.508356910868702</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06434213895971752</v>
+        <v>0.06339593103383932</v>
       </c>
       <c r="W69">
-        <v>0.2206281236332986</v>
+        <v>0.2208512394622207</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2428005243762924</v>
+        <v>0.2392299284295825</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6925,22 +6925,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1857346361913068</v>
+        <v>0.1876346361913068</v>
       </c>
       <c r="C70">
-        <v>-98.62540207705773</v>
+        <v>-100.8508373555439</v>
       </c>
       <c r="D70">
-        <v>27.28059792294227</v>
+        <v>26.93216264445608</v>
       </c>
       <c r="E70">
-        <v>3.73599999999999</v>
+        <v>5.613</v>
       </c>
       <c r="F70">
-        <v>127.636</v>
+        <v>129.513</v>
       </c>
       <c r="G70">
         <v>1.73</v>
@@ -6961,37 +6961,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M70">
-        <v>30.0965688</v>
+        <v>30.5391654</v>
       </c>
       <c r="N70">
-        <v>-22.8965688</v>
+        <v>-23.3391654</v>
       </c>
       <c r="O70">
-        <v>-6.067590731999999</v>
+        <v>-6.184878831</v>
       </c>
       <c r="P70">
-        <v>-16.828978068</v>
+        <v>-17.154286569</v>
       </c>
       <c r="Q70">
-        <v>-1.228978067999998</v>
+        <v>-1.554286569</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1111118542406148</v>
+        <v>0.1132186882483766</v>
       </c>
       <c r="T70">
-        <v>1.508356910868702</v>
+        <v>1.557013585412854</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06339593103383932</v>
+        <v>0.06247714942465325</v>
       </c>
       <c r="W70">
-        <v>0.2208512394622207</v>
+        <v>0.2210678881656668</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2392299284295825</v>
+        <v>0.2357628280175594</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7007,22 +7007,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1876346361913068</v>
+        <v>0.1895346361913068</v>
       </c>
       <c r="C71">
-        <v>-100.8508373555439</v>
+        <v>-103.0674842596843</v>
       </c>
       <c r="D71">
-        <v>26.93216264445608</v>
+        <v>26.59251574031575</v>
       </c>
       <c r="E71">
-        <v>5.613</v>
+        <v>7.490000000000009</v>
       </c>
       <c r="F71">
-        <v>129.513</v>
+        <v>131.39</v>
       </c>
       <c r="G71">
         <v>1.73</v>
@@ -7043,37 +7043,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M71">
-        <v>30.5391654</v>
+        <v>30.981762</v>
       </c>
       <c r="N71">
-        <v>-23.3391654</v>
+        <v>-23.781762</v>
       </c>
       <c r="O71">
-        <v>-6.184878831</v>
+        <v>-6.30216693</v>
       </c>
       <c r="P71">
-        <v>-17.154286569</v>
+        <v>-17.47959507</v>
       </c>
       <c r="Q71">
-        <v>-1.554286569</v>
+        <v>-1.879595070000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1132186882483766</v>
+        <v>0.1154659778566558</v>
       </c>
       <c r="T71">
-        <v>1.557013585412854</v>
+        <v>1.608914038259949</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.06247714942465325</v>
+        <v>0.06158461871858676</v>
       </c>
       <c r="W71">
-        <v>0.2210678881656668</v>
+        <v>0.2212783469061572</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2357628280175594</v>
+        <v>0.2323947876173086</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7089,22 +7089,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1895346361913068</v>
+        <v>0.1914346361913068</v>
       </c>
       <c r="C72">
-        <v>-103.0674842596843</v>
+        <v>-105.2756711443832</v>
       </c>
       <c r="D72">
-        <v>26.59251574031575</v>
+        <v>26.26132885561682</v>
       </c>
       <c r="E72">
-        <v>7.490000000000009</v>
+        <v>9.36699999999999</v>
       </c>
       <c r="F72">
-        <v>131.39</v>
+        <v>133.267</v>
       </c>
       <c r="G72">
         <v>1.73</v>
@@ -7125,37 +7125,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M72">
-        <v>30.981762</v>
+        <v>31.4243586</v>
       </c>
       <c r="N72">
-        <v>-23.781762</v>
+        <v>-24.2243586</v>
       </c>
       <c r="O72">
-        <v>-6.30216693</v>
+        <v>-6.419455029000001</v>
       </c>
       <c r="P72">
-        <v>-17.47959507</v>
+        <v>-17.804903571</v>
       </c>
       <c r="Q72">
-        <v>-1.879595070000002</v>
+        <v>-2.204903571000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1154659778566558</v>
+        <v>0.1178682529551612</v>
       </c>
       <c r="T72">
-        <v>1.608914038259949</v>
+        <v>1.664393832682706</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06158461871858676</v>
+        <v>0.06071722972255034</v>
       </c>
       <c r="W72">
-        <v>0.2212783469061572</v>
+        <v>0.2214828772314227</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2323947876173086</v>
+        <v>0.2291216215945295</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7171,22 +7171,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1914346361913068</v>
+        <v>0.1933346361913068</v>
       </c>
       <c r="C73">
-        <v>-105.2756711443831</v>
+        <v>-107.4757102082474</v>
       </c>
       <c r="D73">
-        <v>26.26132885561686</v>
+        <v>25.93828979175257</v>
       </c>
       <c r="E73">
-        <v>9.36699999999999</v>
+        <v>11.24399999999997</v>
       </c>
       <c r="F73">
-        <v>133.267</v>
+        <v>135.144</v>
       </c>
       <c r="G73">
         <v>1.73</v>
@@ -7207,37 +7207,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M73">
-        <v>31.4243586</v>
+        <v>31.8669552</v>
       </c>
       <c r="N73">
-        <v>-24.2243586</v>
+        <v>-24.6669552</v>
       </c>
       <c r="O73">
-        <v>-6.419455029000001</v>
+        <v>-6.536743127999999</v>
       </c>
       <c r="P73">
-        <v>-17.804903571</v>
+        <v>-18.130212072</v>
       </c>
       <c r="Q73">
-        <v>-2.204903571000001</v>
+        <v>-2.530212071999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1178682529551612</v>
+        <v>0.1204421191321312</v>
       </c>
       <c r="T73">
-        <v>1.664393832682705</v>
+        <v>1.723836469564231</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06071722972255034</v>
+        <v>0.0598739348652927</v>
       </c>
       <c r="W73">
-        <v>0.2214828772314227</v>
+        <v>0.221681726158764</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2291216215945295</v>
+        <v>0.2259393768501611</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7253,22 +7253,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1933346361913068</v>
+        <v>0.1952346361913068</v>
       </c>
       <c r="C74">
-        <v>-107.4757102082474</v>
+        <v>-109.6678984751999</v>
       </c>
       <c r="D74">
-        <v>25.93828979175257</v>
+        <v>25.62310152480007</v>
       </c>
       <c r="E74">
-        <v>11.24399999999997</v>
+        <v>13.12099999999998</v>
       </c>
       <c r="F74">
-        <v>135.144</v>
+        <v>137.021</v>
       </c>
       <c r="G74">
         <v>1.73</v>
@@ -7289,37 +7289,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M74">
-        <v>31.8669552</v>
+        <v>32.3095518</v>
       </c>
       <c r="N74">
-        <v>-24.6669552</v>
+        <v>-25.1095518</v>
       </c>
       <c r="O74">
-        <v>-6.536743127999999</v>
+        <v>-6.654031227</v>
       </c>
       <c r="P74">
-        <v>-18.130212072</v>
+        <v>-18.455520573</v>
       </c>
       <c r="Q74">
-        <v>-2.530212071999999</v>
+        <v>-2.855520572999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1204421191321312</v>
+        <v>0.1232066420629508</v>
       </c>
       <c r="T74">
-        <v>1.723836469564231</v>
+        <v>1.787682264733276</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.0598739348652927</v>
+        <v>0.05905374397672704</v>
       </c>
       <c r="W74">
-        <v>0.221681726158764</v>
+        <v>0.2218751271702878</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2259393768501611</v>
+        <v>0.2228443168933096</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7335,22 +7335,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1952346361913068</v>
+        <v>0.1971346361913068</v>
       </c>
       <c r="C75">
-        <v>-109.6678984751999</v>
+        <v>-111.8525187053839</v>
       </c>
       <c r="D75">
-        <v>25.62310152480007</v>
+        <v>25.31548129461608</v>
       </c>
       <c r="E75">
-        <v>13.12099999999998</v>
+        <v>14.99799999999999</v>
       </c>
       <c r="F75">
-        <v>137.021</v>
+        <v>138.898</v>
       </c>
       <c r="G75">
         <v>1.73</v>
@@ -7371,37 +7371,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M75">
-        <v>32.3095518</v>
+        <v>32.7521484</v>
       </c>
       <c r="N75">
-        <v>-25.1095518</v>
+        <v>-25.5521484</v>
       </c>
       <c r="O75">
-        <v>-6.654031227</v>
+        <v>-6.771319326</v>
       </c>
       <c r="P75">
-        <v>-18.455520573</v>
+        <v>-18.780829074</v>
       </c>
       <c r="Q75">
-        <v>-2.855520572999998</v>
+        <v>-3.180829074</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1232066420629508</v>
+        <v>0.1261838206038336</v>
       </c>
       <c r="T75">
-        <v>1.787682264733276</v>
+        <v>1.856439274915325</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05905374397672704</v>
+        <v>0.05825572040947397</v>
       </c>
       <c r="W75">
-        <v>0.2218751271702878</v>
+        <v>0.222063301127446</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2228443168933096</v>
+        <v>0.2198329072055621</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7417,22 +7417,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1971346361913068</v>
+        <v>0.1990346361913068</v>
       </c>
       <c r="C76">
-        <v>-111.8525187053839</v>
+        <v>-114.0298402412305</v>
       </c>
       <c r="D76">
-        <v>25.31548129461608</v>
+        <v>25.01515975876946</v>
       </c>
       <c r="E76">
-        <v>14.99799999999999</v>
+        <v>16.87499999999997</v>
       </c>
       <c r="F76">
-        <v>138.898</v>
+        <v>140.775</v>
       </c>
       <c r="G76">
         <v>1.73</v>
@@ -7453,37 +7453,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M76">
-        <v>32.7521484</v>
+        <v>33.194745</v>
       </c>
       <c r="N76">
-        <v>-25.5521484</v>
+        <v>-25.99474499999999</v>
       </c>
       <c r="O76">
-        <v>-6.771319326</v>
+        <v>-6.888607424999999</v>
       </c>
       <c r="P76">
-        <v>-18.780829074</v>
+        <v>-19.10613757499999</v>
       </c>
       <c r="Q76">
-        <v>-3.180829074</v>
+        <v>-3.506137574999995</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1261838206038336</v>
+        <v>0.1293991734279869</v>
       </c>
       <c r="T76">
-        <v>1.856439274915325</v>
+        <v>1.930696845911938</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05825572040947397</v>
+        <v>0.05747897747068099</v>
       </c>
       <c r="W76">
-        <v>0.222063301127446</v>
+        <v>0.2222464571124134</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2198329072055621</v>
+        <v>0.2169018017761547</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7499,22 +7499,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1990346361913068</v>
+        <v>0.2009346361913068</v>
       </c>
       <c r="C77">
-        <v>-114.0298402412305</v>
+        <v>-116.2001197940099</v>
       </c>
       <c r="D77">
-        <v>25.01515975876946</v>
+        <v>24.7218802059901</v>
       </c>
       <c r="E77">
-        <v>16.87499999999997</v>
+        <v>18.75199999999998</v>
       </c>
       <c r="F77">
-        <v>140.775</v>
+        <v>142.652</v>
       </c>
       <c r="G77">
         <v>1.73</v>
@@ -7535,37 +7535,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M77">
-        <v>33.194745</v>
+        <v>33.6373416</v>
       </c>
       <c r="N77">
-        <v>-25.99474499999999</v>
+        <v>-26.4373416</v>
       </c>
       <c r="O77">
-        <v>-6.888607424999999</v>
+        <v>-7.005895524</v>
       </c>
       <c r="P77">
-        <v>-19.10613757499999</v>
+        <v>-19.431446076</v>
       </c>
       <c r="Q77">
-        <v>-3.506137574999995</v>
+        <v>-3.831446075999997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1293991734279869</v>
+        <v>0.1328824723208197</v>
       </c>
       <c r="T77">
-        <v>1.930696845911938</v>
+        <v>2.011142547824936</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05747897747068099</v>
+        <v>0.05672267513554045</v>
       </c>
       <c r="W77">
-        <v>0.2222464571124134</v>
+        <v>0.2224247932030396</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2169018017761547</v>
+        <v>0.2140478307001527</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7581,22 +7581,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2009346361913068</v>
+        <v>0.2028346361913068</v>
       </c>
       <c r="C78">
-        <v>-116.2001197940099</v>
+        <v>-118.3636021756939</v>
       </c>
       <c r="D78">
-        <v>24.7218802059901</v>
+        <v>24.43539782430607</v>
       </c>
       <c r="E78">
-        <v>18.75199999999998</v>
+        <v>20.62899999999999</v>
       </c>
       <c r="F78">
-        <v>142.652</v>
+        <v>144.529</v>
       </c>
       <c r="G78">
         <v>1.73</v>
@@ -7617,37 +7617,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M78">
-        <v>33.6373416</v>
+        <v>34.0799382</v>
       </c>
       <c r="N78">
-        <v>-26.4373416</v>
+        <v>-26.8799382</v>
       </c>
       <c r="O78">
-        <v>-7.005895524</v>
+        <v>-7.123183623</v>
       </c>
       <c r="P78">
-        <v>-19.431446076</v>
+        <v>-19.756754577</v>
       </c>
       <c r="Q78">
-        <v>-3.831446075999997</v>
+        <v>-4.156754576999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1328824723208197</v>
+        <v>0.136668666769551</v>
       </c>
       <c r="T78">
-        <v>2.011142547824936</v>
+        <v>2.09858352816515</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05672267513554045</v>
+        <v>0.05598601701689707</v>
       </c>
       <c r="W78">
-        <v>0.2224247932030396</v>
+        <v>0.2225984971874157</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2140478307001527</v>
+        <v>0.2112679887430078</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7663,22 +7663,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2028346361913068</v>
+        <v>0.2047346361913068</v>
       </c>
       <c r="C79">
-        <v>-118.3636021756939</v>
+        <v>-120.5205209805162</v>
       </c>
       <c r="D79">
-        <v>24.43539782430607</v>
+        <v>24.15547901948385</v>
       </c>
       <c r="E79">
-        <v>20.62899999999999</v>
+        <v>22.506</v>
       </c>
       <c r="F79">
-        <v>144.529</v>
+        <v>146.406</v>
       </c>
       <c r="G79">
         <v>1.73</v>
@@ -7699,37 +7699,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M79">
-        <v>34.0799382</v>
+        <v>34.5225348</v>
       </c>
       <c r="N79">
-        <v>-26.8799382</v>
+        <v>-27.3225348</v>
       </c>
       <c r="O79">
-        <v>-7.123183623</v>
+        <v>-7.240471722000001</v>
       </c>
       <c r="P79">
-        <v>-19.756754577</v>
+        <v>-20.082063078</v>
       </c>
       <c r="Q79">
-        <v>-4.156754576999999</v>
+        <v>-4.482063077999998</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.136668666769551</v>
+        <v>0.1407990607136215</v>
       </c>
       <c r="T79">
-        <v>2.09858352816515</v>
+        <v>2.193973688536294</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05598601701689707</v>
+        <v>0.05526824756796248</v>
       </c>
       <c r="W79">
-        <v>0.2225984971874157</v>
+        <v>0.2227677472234745</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2112679887430078</v>
+        <v>0.2085594247847641</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7745,22 +7745,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2047346361913068</v>
+        <v>0.2066346361913068</v>
       </c>
       <c r="C80">
-        <v>-120.5205209805162</v>
+        <v>-122.6710992202169</v>
       </c>
       <c r="D80">
-        <v>24.15547901948385</v>
+        <v>23.88190077978311</v>
       </c>
       <c r="E80">
-        <v>22.506</v>
+        <v>24.38299999999998</v>
       </c>
       <c r="F80">
-        <v>146.406</v>
+        <v>148.283</v>
       </c>
       <c r="G80">
         <v>1.73</v>
@@ -7781,37 +7781,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M80">
-        <v>34.5225348</v>
+        <v>34.9651314</v>
       </c>
       <c r="N80">
-        <v>-27.3225348</v>
+        <v>-27.76513139999999</v>
       </c>
       <c r="O80">
-        <v>-7.240471722000001</v>
+        <v>-7.357759820999999</v>
       </c>
       <c r="P80">
-        <v>-20.082063078</v>
+        <v>-20.407371579</v>
       </c>
       <c r="Q80">
-        <v>-4.482063077999998</v>
+        <v>-4.807371578999996</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1407990607136215</v>
+        <v>0.1453228255095083</v>
       </c>
       <c r="T80">
-        <v>2.193973688536294</v>
+        <v>2.298448626085641</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05526824756796248</v>
+        <v>0.05456864949748196</v>
       </c>
       <c r="W80">
-        <v>0.2227677472234745</v>
+        <v>0.2229327124484937</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2085594247847641</v>
+        <v>0.2059194320659696</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7827,22 +7827,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2066346361913068</v>
+        <v>0.2085346361913068</v>
       </c>
       <c r="C81">
-        <v>-122.6710992202169</v>
+        <v>-124.8155499166036</v>
       </c>
       <c r="D81">
-        <v>23.88190077978311</v>
+        <v>23.61445008339637</v>
       </c>
       <c r="E81">
-        <v>24.38299999999998</v>
+        <v>26.25999999999999</v>
       </c>
       <c r="F81">
-        <v>148.283</v>
+        <v>150.16</v>
       </c>
       <c r="G81">
         <v>1.73</v>
@@ -7863,37 +7863,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M81">
-        <v>34.9651314</v>
+        <v>35.407728</v>
       </c>
       <c r="N81">
-        <v>-27.76513139999999</v>
+        <v>-28.207728</v>
       </c>
       <c r="O81">
-        <v>-7.357759820999999</v>
+        <v>-7.47504792</v>
       </c>
       <c r="P81">
-        <v>-20.407371579</v>
+        <v>-20.73268007999999</v>
       </c>
       <c r="Q81">
-        <v>-4.807371578999996</v>
+        <v>-5.132680079999995</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1453228255095083</v>
+        <v>0.1502989667849837</v>
       </c>
       <c r="T81">
-        <v>2.298448626085641</v>
+        <v>2.413371057389923</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05456864949748196</v>
+        <v>0.05388654137876343</v>
       </c>
       <c r="W81">
-        <v>0.2229327124484937</v>
+        <v>0.2230935535428876</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2059194320659696</v>
+        <v>0.203345439165145</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7909,22 +7909,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2085346361913068</v>
+        <v>0.2104346361913068</v>
       </c>
       <c r="C82">
-        <v>-124.8155499166036</v>
+        <v>-126.9540766547368</v>
       </c>
       <c r="D82">
-        <v>23.61445008339637</v>
+        <v>23.35292334526317</v>
       </c>
       <c r="E82">
-        <v>26.25999999999999</v>
+        <v>28.137</v>
       </c>
       <c r="F82">
-        <v>150.16</v>
+        <v>152.037</v>
       </c>
       <c r="G82">
         <v>1.73</v>
@@ -7945,37 +7945,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M82">
-        <v>35.407728</v>
+        <v>35.8503246</v>
       </c>
       <c r="N82">
-        <v>-28.207728</v>
+        <v>-28.6503246</v>
       </c>
       <c r="O82">
-        <v>-7.47504792</v>
+        <v>-7.592336018999999</v>
       </c>
       <c r="P82">
-        <v>-20.73268007999999</v>
+        <v>-21.057988581</v>
       </c>
       <c r="Q82">
-        <v>-5.132680079999995</v>
+        <v>-5.457988580999997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1502989667849837</v>
+        <v>0.155798912405246</v>
       </c>
       <c r="T82">
-        <v>2.413371057389923</v>
+        <v>2.540390586726236</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05388654137876343</v>
+        <v>0.05322127543581573</v>
       </c>
       <c r="W82">
-        <v>0.2230935535428876</v>
+        <v>0.2232504232522347</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.203345439165145</v>
+        <v>0.2008350016445877</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -7991,22 +7991,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2104346361913068</v>
+        <v>0.2123346361913068</v>
       </c>
       <c r="C83">
-        <v>-126.9540766547368</v>
+        <v>-129.0868740997592</v>
       </c>
       <c r="D83">
-        <v>23.35292334526317</v>
+        <v>23.09712590024082</v>
       </c>
       <c r="E83">
-        <v>28.137</v>
+        <v>30.01400000000001</v>
       </c>
       <c r="F83">
-        <v>152.037</v>
+        <v>153.914</v>
       </c>
       <c r="G83">
         <v>1.73</v>
@@ -8027,37 +8027,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M83">
-        <v>35.8503246</v>
+        <v>36.2929212</v>
       </c>
       <c r="N83">
-        <v>-28.6503246</v>
+        <v>-29.0929212</v>
       </c>
       <c r="O83">
-        <v>-7.592336018999999</v>
+        <v>-7.709624118</v>
       </c>
       <c r="P83">
-        <v>-21.057988581</v>
+        <v>-21.383297082</v>
       </c>
       <c r="Q83">
-        <v>-5.457988580999997</v>
+        <v>-5.783297081999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.155798912405246</v>
+        <v>0.1619099630944263</v>
       </c>
       <c r="T83">
-        <v>2.540390586726236</v>
+        <v>2.681523397099915</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05322127543581573</v>
+        <v>0.05257223549147651</v>
       </c>
       <c r="W83">
-        <v>0.2232504232522347</v>
+        <v>0.2234034668711098</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2008350016445877</v>
+        <v>0.1983857943074586</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8073,22 +8073,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2123346361913068</v>
+        <v>0.2142346361913068</v>
       </c>
       <c r="C84">
-        <v>-129.0868740997592</v>
+        <v>-131.2141284801267</v>
       </c>
       <c r="D84">
-        <v>23.09712590024082</v>
+        <v>22.8468715198733</v>
       </c>
       <c r="E84">
-        <v>30.01400000000001</v>
+        <v>31.89099999999999</v>
       </c>
       <c r="F84">
-        <v>153.914</v>
+        <v>155.791</v>
       </c>
       <c r="G84">
         <v>1.73</v>
@@ -8109,37 +8109,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M84">
-        <v>36.2929212</v>
+        <v>36.7355178</v>
       </c>
       <c r="N84">
-        <v>-29.0929212</v>
+        <v>-29.5355178</v>
       </c>
       <c r="O84">
-        <v>-7.709624118</v>
+        <v>-7.826912217</v>
       </c>
       <c r="P84">
-        <v>-21.383297082</v>
+        <v>-21.708605583</v>
       </c>
       <c r="Q84">
-        <v>-5.783297081999999</v>
+        <v>-6.108605583000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1619099630944263</v>
+        <v>0.1687399609235102</v>
       </c>
       <c r="T84">
-        <v>2.681523397099915</v>
+        <v>2.839260067517558</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05257223549147651</v>
+        <v>0.05193883506386836</v>
       </c>
       <c r="W84">
-        <v>0.2234034668711098</v>
+        <v>0.2235528226919399</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1983857943074586</v>
+        <v>0.1959956040145976</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8155,22 +8155,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2142346361913068</v>
+        <v>0.2161346361913068</v>
       </c>
       <c r="C85">
-        <v>-131.2141284801267</v>
+        <v>-133.3360180397614</v>
       </c>
       <c r="D85">
-        <v>22.8468715198733</v>
+        <v>22.60198196023863</v>
       </c>
       <c r="E85">
-        <v>31.89099999999999</v>
+        <v>33.768</v>
       </c>
       <c r="F85">
-        <v>155.791</v>
+        <v>157.668</v>
       </c>
       <c r="G85">
         <v>1.73</v>
@@ -8191,37 +8191,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M85">
-        <v>36.7355178</v>
+        <v>37.17811440000001</v>
       </c>
       <c r="N85">
-        <v>-29.5355178</v>
+        <v>-29.9781144</v>
       </c>
       <c r="O85">
-        <v>-7.826912217</v>
+        <v>-7.944200316000001</v>
       </c>
       <c r="P85">
-        <v>-21.708605583</v>
+        <v>-22.033914084</v>
       </c>
       <c r="Q85">
-        <v>-6.108605583000001</v>
+        <v>-6.433914084000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1687399609235102</v>
+        <v>0.1764237084812297</v>
       </c>
       <c r="T85">
-        <v>2.839260067517558</v>
+        <v>3.016713821737405</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05193883506386836</v>
+        <v>0.0513205155988223</v>
       </c>
       <c r="W85">
-        <v>0.2235528226919399</v>
+        <v>0.2236986224217977</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1959956040145976</v>
+        <v>0.1936623230144239</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8237,22 +8237,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2161346361913068</v>
+        <v>0.2180346361913068</v>
       </c>
       <c r="C86">
-        <v>-133.3360180397613</v>
+        <v>-135.4527134614339</v>
       </c>
       <c r="D86">
-        <v>22.60198196023867</v>
+        <v>22.36228653856612</v>
       </c>
       <c r="E86">
-        <v>33.76799999999997</v>
+        <v>35.64499999999998</v>
       </c>
       <c r="F86">
-        <v>157.668</v>
+        <v>159.545</v>
       </c>
       <c r="G86">
         <v>1.73</v>
@@ -8273,37 +8273,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M86">
-        <v>37.1781144</v>
+        <v>37.620711</v>
       </c>
       <c r="N86">
-        <v>-29.9781144</v>
+        <v>-30.420711</v>
       </c>
       <c r="O86">
-        <v>-7.944200315999999</v>
+        <v>-8.061488414999999</v>
       </c>
       <c r="P86">
-        <v>-22.033914084</v>
+        <v>-22.359222585</v>
       </c>
       <c r="Q86">
-        <v>-6.433914083999996</v>
+        <v>-6.759222584999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1764237084812296</v>
+        <v>0.1851319557133115</v>
       </c>
       <c r="T86">
-        <v>3.016713821737403</v>
+        <v>3.217828076519897</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05132051559882232</v>
+        <v>0.05071674482707146</v>
       </c>
       <c r="W86">
-        <v>0.2236986224217977</v>
+        <v>0.2238409915697765</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1936623230144239</v>
+        <v>0.1913839427436659</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8319,22 +8319,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2180346361913068</v>
+        <v>0.2199346361913068</v>
       </c>
       <c r="C87">
-        <v>-135.4527134614339</v>
+        <v>-137.5643782634885</v>
       </c>
       <c r="D87">
-        <v>22.36228653856612</v>
+        <v>22.12762173651147</v>
       </c>
       <c r="E87">
-        <v>35.64499999999998</v>
+        <v>37.52199999999999</v>
       </c>
       <c r="F87">
-        <v>159.545</v>
+        <v>161.422</v>
       </c>
       <c r="G87">
         <v>1.73</v>
@@ -8355,37 +8355,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M87">
-        <v>37.620711</v>
+        <v>38.0633076</v>
       </c>
       <c r="N87">
-        <v>-30.420711</v>
+        <v>-30.8633076</v>
       </c>
       <c r="O87">
-        <v>-8.061488414999999</v>
+        <v>-8.178776514000001</v>
       </c>
       <c r="P87">
-        <v>-22.359222585</v>
+        <v>-22.684531086</v>
       </c>
       <c r="Q87">
-        <v>-6.759222584999998</v>
+        <v>-7.084531086</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1851319557133115</v>
+        <v>0.1950842382642624</v>
       </c>
       <c r="T87">
-        <v>3.217828076519897</v>
+        <v>3.447672939128461</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05071674482707146</v>
+        <v>0.050127015236059</v>
       </c>
       <c r="W87">
-        <v>0.2238409915697765</v>
+        <v>0.2239800498073373</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1913839427436659</v>
+        <v>0.1891585480606001</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8401,22 +8401,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2199346361913068</v>
+        <v>0.2218346361913068</v>
       </c>
       <c r="C88">
-        <v>-137.5643782634885</v>
+        <v>-139.671169171849</v>
       </c>
       <c r="D88">
-        <v>22.12762173651147</v>
+        <v>21.89783082815093</v>
       </c>
       <c r="E88">
-        <v>37.52199999999999</v>
+        <v>39.39899999999997</v>
       </c>
       <c r="F88">
-        <v>161.422</v>
+        <v>163.299</v>
       </c>
       <c r="G88">
         <v>1.73</v>
@@ -8437,37 +8437,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M88">
-        <v>38.0633076</v>
+        <v>38.5059042</v>
       </c>
       <c r="N88">
-        <v>-30.8633076</v>
+        <v>-31.30590419999999</v>
       </c>
       <c r="O88">
-        <v>-8.178776514000001</v>
+        <v>-8.296064612999999</v>
       </c>
       <c r="P88">
-        <v>-22.684531086</v>
+        <v>-23.00983958699999</v>
       </c>
       <c r="Q88">
-        <v>-7.084531086</v>
+        <v>-7.409839586999995</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1950842382642624</v>
+        <v>0.2065676412076672</v>
       </c>
       <c r="T88">
-        <v>3.447672939128461</v>
+        <v>3.71287854983065</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.050127015236059</v>
+        <v>0.04955084264713879</v>
       </c>
       <c r="W88">
-        <v>0.2239800498073373</v>
+        <v>0.2241159113038047</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1891585480606001</v>
+        <v>0.1869843118759955</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8483,22 +8483,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2218346361913068</v>
+        <v>0.2237346361913068</v>
       </c>
       <c r="C89">
-        <v>-139.671169171849</v>
+        <v>-141.773236469083</v>
       </c>
       <c r="D89">
-        <v>21.89783082815093</v>
+        <v>21.67276353091701</v>
       </c>
       <c r="E89">
-        <v>39.39899999999997</v>
+        <v>41.27599999999998</v>
       </c>
       <c r="F89">
-        <v>163.299</v>
+        <v>165.176</v>
       </c>
       <c r="G89">
         <v>1.73</v>
@@ -8519,37 +8519,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M89">
-        <v>38.5059042</v>
+        <v>38.9485008</v>
       </c>
       <c r="N89">
-        <v>-31.30590419999999</v>
+        <v>-31.7485008</v>
       </c>
       <c r="O89">
-        <v>-8.296064612999999</v>
+        <v>-8.413352711999998</v>
       </c>
       <c r="P89">
-        <v>-23.00983958699999</v>
+        <v>-23.335148088</v>
       </c>
       <c r="Q89">
-        <v>-7.409839586999995</v>
+        <v>-7.735148087999997</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2065676412076672</v>
+        <v>0.2199649446416394</v>
       </c>
       <c r="T89">
-        <v>3.71287854983065</v>
+        <v>4.022285095649871</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04955084264713879</v>
+        <v>0.04898776488978493</v>
       </c>
       <c r="W89">
-        <v>0.2241159113038047</v>
+        <v>0.2242486850389887</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1869843118759955</v>
+        <v>0.1848594901501319</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8565,22 +8565,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2237346361913068</v>
+        <v>0.2256346361913068</v>
       </c>
       <c r="C90">
-        <v>-141.773236469083</v>
+        <v>-143.8707243221594</v>
       </c>
       <c r="D90">
-        <v>21.67276353091701</v>
+        <v>21.45227567784056</v>
       </c>
       <c r="E90">
-        <v>41.27599999999998</v>
+        <v>43.15299999999999</v>
       </c>
       <c r="F90">
-        <v>165.176</v>
+        <v>167.053</v>
       </c>
       <c r="G90">
         <v>1.73</v>
@@ -8601,37 +8601,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M90">
-        <v>38.9485008</v>
+        <v>39.3910974</v>
       </c>
       <c r="N90">
-        <v>-31.7485008</v>
+        <v>-32.1910974</v>
       </c>
       <c r="O90">
-        <v>-8.413352711999998</v>
+        <v>-8.530640811</v>
       </c>
       <c r="P90">
-        <v>-23.335148088</v>
+        <v>-23.660456589</v>
       </c>
       <c r="Q90">
-        <v>-7.735148087999997</v>
+        <v>-8.060456588999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2199649446416394</v>
+        <v>0.235798121427243</v>
       </c>
       <c r="T90">
-        <v>4.022285095649871</v>
+        <v>4.387947377072588</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04898776488978493</v>
+        <v>0.04843734056518061</v>
       </c>
       <c r="W90">
-        <v>0.2242486850389887</v>
+        <v>0.2243784750947304</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1848594901501319</v>
+        <v>0.1827824172270966</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8647,22 +8647,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2256346361913068</v>
+        <v>0.2275346361913068</v>
       </c>
       <c r="C91">
-        <v>-143.8707243221594</v>
+        <v>-145.9637710904009</v>
       </c>
       <c r="D91">
-        <v>21.45227567784056</v>
+        <v>21.23622890959911</v>
       </c>
       <c r="E91">
-        <v>43.15299999999999</v>
+        <v>45.03</v>
       </c>
       <c r="F91">
-        <v>167.053</v>
+        <v>168.93</v>
       </c>
       <c r="G91">
         <v>1.73</v>
@@ -8683,37 +8683,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M91">
-        <v>39.3910974</v>
+        <v>39.833694</v>
       </c>
       <c r="N91">
-        <v>-32.1910974</v>
+        <v>-32.633694</v>
       </c>
       <c r="O91">
-        <v>-8.530640811</v>
+        <v>-8.647928909999999</v>
       </c>
       <c r="P91">
-        <v>-23.660456589</v>
+        <v>-23.98576509</v>
       </c>
       <c r="Q91">
-        <v>-8.060456588999999</v>
+        <v>-8.385765090000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.235798121427243</v>
+        <v>0.2547979335699673</v>
       </c>
       <c r="T91">
-        <v>4.387947377072588</v>
+        <v>4.826742114779846</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04843734056518061</v>
+        <v>0.04789914789223416</v>
       </c>
       <c r="W91">
-        <v>0.2243784750947304</v>
+        <v>0.2245053809270112</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1827824172270966</v>
+        <v>0.180751501480129</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8729,22 +8729,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2275346361913068</v>
+        <v>0.2294346361913068</v>
       </c>
       <c r="C92">
-        <v>-145.9637710904009</v>
+        <v>-148.0525096150131</v>
       </c>
       <c r="D92">
-        <v>21.23622890959911</v>
+        <v>21.02449038498688</v>
       </c>
       <c r="E92">
-        <v>45.03</v>
+        <v>46.90699999999998</v>
       </c>
       <c r="F92">
-        <v>168.93</v>
+        <v>170.807</v>
       </c>
       <c r="G92">
         <v>1.73</v>
@@ -8765,37 +8765,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M92">
-        <v>39.833694</v>
+        <v>40.2762906</v>
       </c>
       <c r="N92">
-        <v>-32.633694</v>
+        <v>-33.07629059999999</v>
       </c>
       <c r="O92">
-        <v>-8.647928909999999</v>
+        <v>-8.765217008999999</v>
       </c>
       <c r="P92">
-        <v>-23.98576509</v>
+        <v>-24.311073591</v>
       </c>
       <c r="Q92">
-        <v>-8.385765090000001</v>
+        <v>-8.711073590999996</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2547979335699673</v>
+        <v>0.2780199261888526</v>
       </c>
       <c r="T92">
-        <v>4.826742114779846</v>
+        <v>5.36304679419983</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04789914789223416</v>
+        <v>0.04737278362968214</v>
       </c>
       <c r="W92">
-        <v>0.2245053809270112</v>
+        <v>0.224629497620121</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.180751501480129</v>
+        <v>0.1787652212440836</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8811,22 +8811,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2294346361913068</v>
+        <v>0.2313346361913068</v>
       </c>
       <c r="C93">
-        <v>-148.0525096150131</v>
+        <v>-150.1370674914644</v>
       </c>
       <c r="D93">
-        <v>21.02449038498688</v>
+        <v>20.81693250853561</v>
       </c>
       <c r="E93">
-        <v>46.90699999999998</v>
+        <v>48.78399999999999</v>
       </c>
       <c r="F93">
-        <v>170.807</v>
+        <v>172.684</v>
       </c>
       <c r="G93">
         <v>1.73</v>
@@ -8847,37 +8847,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M93">
-        <v>40.2762906</v>
+        <v>40.7188872</v>
       </c>
       <c r="N93">
-        <v>-33.07629059999999</v>
+        <v>-33.5188872</v>
       </c>
       <c r="O93">
-        <v>-8.765217008999999</v>
+        <v>-8.882505108</v>
       </c>
       <c r="P93">
-        <v>-24.311073591</v>
+        <v>-24.636382092</v>
       </c>
       <c r="Q93">
-        <v>-8.711073590999996</v>
+        <v>-9.036382092000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2780199261888526</v>
+        <v>0.3070474169624593</v>
       </c>
       <c r="T93">
-        <v>5.36304679419983</v>
+        <v>6.033427643474811</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04737278362968214</v>
+        <v>0.04685786206848993</v>
       </c>
       <c r="W93">
-        <v>0.224629497620121</v>
+        <v>0.2247509161242501</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1787652212440836</v>
+        <v>0.1768221210131696</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8893,22 +8893,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2313346361913068</v>
+        <v>0.2332346361913068</v>
       </c>
       <c r="C94">
-        <v>-150.1370674914644</v>
+        <v>-152.2175673258892</v>
       </c>
       <c r="D94">
-        <v>20.81693250853561</v>
+        <v>20.61343267411083</v>
       </c>
       <c r="E94">
-        <v>48.78399999999999</v>
+        <v>50.661</v>
       </c>
       <c r="F94">
-        <v>172.684</v>
+        <v>174.561</v>
       </c>
       <c r="G94">
         <v>1.73</v>
@@ -8929,37 +8929,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M94">
-        <v>40.7188872</v>
+        <v>41.16148380000001</v>
       </c>
       <c r="N94">
-        <v>-33.5188872</v>
+        <v>-33.9614838</v>
       </c>
       <c r="O94">
-        <v>-8.882505108</v>
+        <v>-8.999793207000002</v>
       </c>
       <c r="P94">
-        <v>-24.636382092</v>
+        <v>-24.961690593</v>
       </c>
       <c r="Q94">
-        <v>-9.036382092000002</v>
+        <v>-9.361690593000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3070474169624593</v>
+        <v>0.344368476528525</v>
       </c>
       <c r="T94">
-        <v>6.033427643474811</v>
+        <v>6.895345878256927</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04685786206848993</v>
+        <v>0.04635401408925886</v>
       </c>
       <c r="W94">
-        <v>0.2247509161242501</v>
+        <v>0.2248697234777528</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1768221210131696</v>
+        <v>0.1749208078839957</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8975,22 +8975,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2332346361913068</v>
+        <v>0.2351346361913068</v>
       </c>
       <c r="C95">
-        <v>-152.2175673258892</v>
+        <v>-154.2941269765978</v>
       </c>
       <c r="D95">
-        <v>20.61343267411083</v>
+        <v>20.41387302340216</v>
       </c>
       <c r="E95">
-        <v>50.661</v>
+        <v>52.53799999999998</v>
       </c>
       <c r="F95">
-        <v>174.561</v>
+        <v>176.438</v>
       </c>
       <c r="G95">
         <v>1.73</v>
@@ -9011,37 +9011,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M95">
-        <v>41.16148380000001</v>
+        <v>41.6040804</v>
       </c>
       <c r="N95">
-        <v>-33.9614838</v>
+        <v>-34.4040804</v>
       </c>
       <c r="O95">
-        <v>-8.999793207000002</v>
+        <v>-9.117081305999999</v>
       </c>
       <c r="P95">
-        <v>-24.961690593</v>
+        <v>-25.286999094</v>
       </c>
       <c r="Q95">
-        <v>-9.361690593000001</v>
+        <v>-9.686999093999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.344368476528525</v>
+        <v>0.3941298892832792</v>
       </c>
       <c r="T95">
-        <v>6.895345878256927</v>
+        <v>8.044570191299751</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04635401408925886</v>
+        <v>0.04586088627979866</v>
       </c>
       <c r="W95">
-        <v>0.2248697234777528</v>
+        <v>0.2249860030152235</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1749208078839957</v>
+        <v>0.1730599482256554</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9057,22 +9057,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2351346361913068</v>
+        <v>0.2370346361913068</v>
       </c>
       <c r="C96">
-        <v>-154.2941269765978</v>
+        <v>-156.3668597816931</v>
       </c>
       <c r="D96">
-        <v>20.41387302340216</v>
+        <v>20.21814021830694</v>
       </c>
       <c r="E96">
-        <v>52.53799999999998</v>
+        <v>54.41499999999999</v>
       </c>
       <c r="F96">
-        <v>176.438</v>
+        <v>178.315</v>
       </c>
       <c r="G96">
         <v>1.73</v>
@@ -9093,37 +9093,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M96">
-        <v>41.6040804</v>
+        <v>42.046677</v>
       </c>
       <c r="N96">
-        <v>-34.4040804</v>
+        <v>-34.846677</v>
       </c>
       <c r="O96">
-        <v>-9.117081305999999</v>
+        <v>-9.234369405000001</v>
       </c>
       <c r="P96">
-        <v>-25.286999094</v>
+        <v>-25.612307595</v>
       </c>
       <c r="Q96">
-        <v>-9.686999093999999</v>
+        <v>-10.012307595</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3941298892832792</v>
+        <v>0.4637958671399352</v>
       </c>
       <c r="T96">
-        <v>8.044570191299751</v>
+        <v>9.653484229559705</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04586088627979866</v>
+        <v>0.04537814010843236</v>
       </c>
       <c r="W96">
-        <v>0.2249860030152235</v>
+        <v>0.2250998345624317</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1730599482256554</v>
+        <v>0.1712382645601221</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9139,22 +9139,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2370346361913068</v>
+        <v>0.2389346361913068</v>
       </c>
       <c r="C97">
-        <v>-156.3668597816931</v>
+        <v>-158.4358747737152</v>
       </c>
       <c r="D97">
-        <v>20.21814021830694</v>
+        <v>20.02612522628482</v>
       </c>
       <c r="E97">
-        <v>54.41499999999999</v>
+        <v>56.292</v>
       </c>
       <c r="F97">
-        <v>178.315</v>
+        <v>180.192</v>
       </c>
       <c r="G97">
         <v>1.73</v>
@@ -9175,37 +9175,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M97">
-        <v>42.046677</v>
+        <v>42.4892736</v>
       </c>
       <c r="N97">
-        <v>-34.846677</v>
+        <v>-35.2892736</v>
       </c>
       <c r="O97">
-        <v>-9.234369405000001</v>
+        <v>-9.351657504</v>
       </c>
       <c r="P97">
-        <v>-25.612307595</v>
+        <v>-25.937616096</v>
       </c>
       <c r="Q97">
-        <v>-10.012307595</v>
+        <v>-10.337616096</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4637958671399352</v>
+        <v>0.5682948339249192</v>
       </c>
       <c r="T97">
-        <v>9.653484229559705</v>
+        <v>12.06685528694964</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04537814010843236</v>
+        <v>0.04490545114896952</v>
       </c>
       <c r="W97">
-        <v>0.2250998345624317</v>
+        <v>0.225211294619073</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1712382645601221</v>
+        <v>0.1694545326376209</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9221,22 +9221,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2389346361913068</v>
+        <v>0.2408346361913068</v>
       </c>
       <c r="C98">
-        <v>-158.4358747737152</v>
+        <v>-160.5012768821721</v>
       </c>
       <c r="D98">
-        <v>20.0261252262848</v>
+        <v>19.83772311782791</v>
       </c>
       <c r="E98">
-        <v>56.29199999999997</v>
+        <v>58.16899999999998</v>
       </c>
       <c r="F98">
-        <v>180.192</v>
+        <v>182.069</v>
       </c>
       <c r="G98">
         <v>1.73</v>
@@ -9257,37 +9257,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M98">
-        <v>42.4892736</v>
+        <v>42.9318702</v>
       </c>
       <c r="N98">
-        <v>-35.28927359999999</v>
+        <v>-35.7318702</v>
       </c>
       <c r="O98">
-        <v>-9.351657503999999</v>
+        <v>-9.468945603</v>
       </c>
       <c r="P98">
-        <v>-25.937616096</v>
+        <v>-26.26292459699999</v>
       </c>
       <c r="Q98">
-        <v>-10.337616096</v>
+        <v>-10.66292459699999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5682948339249179</v>
+        <v>0.7424597785665572</v>
       </c>
       <c r="T98">
-        <v>12.06685528694961</v>
+        <v>16.08914038259947</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04490545114896952</v>
+        <v>0.04444250835361932</v>
       </c>
       <c r="W98">
-        <v>0.225211294619073</v>
+        <v>0.2253204565302166</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1694545326376209</v>
+        <v>0.1677075786929031</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9303,22 +9303,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2408346361913068</v>
+        <v>0.2427346361913068</v>
       </c>
       <c r="C99">
-        <v>-160.5012768821721</v>
+        <v>-162.5631671247433</v>
       </c>
       <c r="D99">
-        <v>19.83772311782791</v>
+        <v>19.65283287525668</v>
       </c>
       <c r="E99">
-        <v>58.16899999999998</v>
+        <v>60.04599999999999</v>
       </c>
       <c r="F99">
-        <v>182.069</v>
+        <v>183.946</v>
       </c>
       <c r="G99">
         <v>1.73</v>
@@ -9339,37 +9339,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M99">
-        <v>42.9318702</v>
+        <v>43.3744668</v>
       </c>
       <c r="N99">
-        <v>-35.7318702</v>
+        <v>-36.1744668</v>
       </c>
       <c r="O99">
-        <v>-9.468945603</v>
+        <v>-9.586233701999999</v>
       </c>
       <c r="P99">
-        <v>-26.26292459699999</v>
+        <v>-26.588233098</v>
       </c>
       <c r="Q99">
-        <v>-10.66292459699999</v>
+        <v>-10.988233098</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7424597785665572</v>
+        <v>1.090789667849836</v>
       </c>
       <c r="T99">
-        <v>16.08914038259947</v>
+        <v>24.13371057389921</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04444250835361932</v>
+        <v>0.04398901337041912</v>
       </c>
       <c r="W99">
-        <v>0.2253204565302166</v>
+        <v>0.2254273906472552</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1677075786929031</v>
+        <v>0.1659962768695061</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9385,22 +9385,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2427346361913068</v>
+        <v>0.2446346361913068</v>
       </c>
       <c r="C100">
-        <v>-162.5631671247433</v>
+        <v>-164.6216427878905</v>
       </c>
       <c r="D100">
-        <v>19.65283287525668</v>
+        <v>19.47135721210949</v>
       </c>
       <c r="E100">
-        <v>60.04599999999999</v>
+        <v>61.92299999999997</v>
       </c>
       <c r="F100">
-        <v>183.946</v>
+        <v>185.823</v>
       </c>
       <c r="G100">
         <v>1.73</v>
@@ -9421,37 +9421,37 @@
         <v>7.200000000000001</v>
       </c>
       <c r="M100">
-        <v>43.3744668</v>
+        <v>43.81706339999999</v>
       </c>
       <c r="N100">
-        <v>-36.1744668</v>
+        <v>-36.61706339999999</v>
       </c>
       <c r="O100">
-        <v>-9.586233701999999</v>
+        <v>-9.703521800999999</v>
       </c>
       <c r="P100">
-        <v>-26.588233098</v>
+        <v>-26.91354159899999</v>
       </c>
       <c r="Q100">
-        <v>-10.988233098</v>
+        <v>-11.31354159899999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.090789667849836</v>
+        <v>2.135779335699671</v>
       </c>
       <c r="T100">
-        <v>24.13371057389921</v>
+        <v>48.26742114779842</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04398901337041912</v>
+        <v>0.04354467990203106</v>
       </c>
       <c r="W100">
-        <v>0.2254273906472552</v>
+        <v>0.2255321644791011</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9459,91 +9459,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1659962768695061</v>
+        <v>0.1643195468001172</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2446346361913068</v>
-      </c>
-      <c r="C101">
-        <v>-164.6216427878905</v>
-      </c>
-      <c r="D101">
-        <v>19.47135721210949</v>
-      </c>
-      <c r="E101">
-        <v>61.92299999999997</v>
-      </c>
-      <c r="F101">
-        <v>185.823</v>
-      </c>
-      <c r="G101">
-        <v>1.73</v>
-      </c>
-      <c r="H101">
-        <v>63.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.8</v>
-      </c>
-      <c r="K101">
-        <v>15.6</v>
-      </c>
-      <c r="L101">
-        <v>7.200000000000001</v>
-      </c>
-      <c r="M101">
-        <v>43.81706339999999</v>
-      </c>
-      <c r="N101">
-        <v>-36.61706339999999</v>
-      </c>
-      <c r="O101">
-        <v>-9.703521800999999</v>
-      </c>
-      <c r="P101">
-        <v>-26.91354159899999</v>
-      </c>
-      <c r="Q101">
-        <v>-11.31354159899999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.135779335699671</v>
-      </c>
-      <c r="T101">
-        <v>48.26742114779842</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04354467990203106</v>
-      </c>
-      <c r="W101">
-        <v>0.2255321644791011</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1643195468001172</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
